--- a/brazil/budget_layer_all_years.xlsx
+++ b/brazil/budget_layer_all_years.xlsx
@@ -416,7 +416,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L211"/>
+  <dimension ref="A1:N211"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -472,10 +472,20 @@
       </c>
       <c r="K1" t="inlineStr">
         <is>
+          <t>programme_class</t>
+        </is>
+      </c>
+      <c r="L1" t="inlineStr">
+        <is>
+          <t>class_source</t>
+        </is>
+      </c>
+      <c r="M1" t="inlineStr">
+        <is>
           <t>strategy_name_source</t>
         </is>
       </c>
-      <c r="L1" t="inlineStr">
+      <c r="N1" t="inlineStr">
         <is>
           <t>program_name_source</t>
         </is>
@@ -520,11 +530,6 @@
           <t>/Users/sebastianpasha/Developer/Environment_UNDP/PV2/Files/llm/brazil/brazil_budget_2024.xlsx</t>
         </is>
       </c>
-      <c r="K2" t="inlineStr">
-        <is>
-          <t>Judiciária</t>
-        </is>
-      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -577,10 +582,15 @@
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>Judiciária</t>
+          <t>standing_function</t>
         </is>
       </c>
       <c r="L3" t="inlineStr">
+        <is>
+          <t>model</t>
+        </is>
+      </c>
+      <c r="N3" t="inlineStr">
         <is>
           <t>PROGRAMA DE GESTAO E MANUTENCAO DO PODER JUDICIARIO</t>
         </is>
@@ -625,11 +635,6 @@
           <t>/Users/sebastianpasha/Developer/Environment_UNDP/PV2/Files/llm/brazil/brazil_budget_2024.xlsx</t>
         </is>
       </c>
-      <c r="K4" t="inlineStr">
-        <is>
-          <t>Essencial à justiça</t>
-        </is>
-      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -682,10 +687,15 @@
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>Essencial à justiça</t>
+          <t>standing_function</t>
         </is>
       </c>
       <c r="L5" t="inlineStr">
+        <is>
+          <t>model</t>
+        </is>
+      </c>
+      <c r="N5" t="inlineStr">
         <is>
           <t>PROGRAMA DE GESTAO E MANUTENCAO DO PODER EXECUTIVO</t>
         </is>
@@ -742,10 +752,15 @@
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>Essencial à justiça</t>
+          <t>development</t>
         </is>
       </c>
       <c r="L6" t="inlineStr">
+        <is>
+          <t>model</t>
+        </is>
+      </c>
+      <c r="N6" t="inlineStr">
         <is>
           <t>DEFESA DA DEMOCRACIA E SEGURANCA JURIDICA PARA INOVACAOEM PO</t>
         </is>
@@ -790,11 +805,6 @@
           <t>/Users/sebastianpasha/Developer/Environment_UNDP/PV2/Files/llm/brazil/brazil_budget_2024.xlsx</t>
         </is>
       </c>
-      <c r="K7" t="inlineStr">
-        <is>
-          <t>Administração</t>
-        </is>
-      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -847,10 +857,15 @@
       </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t>Administração</t>
+          <t>standing_function</t>
         </is>
       </c>
       <c r="L8" t="inlineStr">
+        <is>
+          <t>model</t>
+        </is>
+      </c>
+      <c r="N8" t="inlineStr">
         <is>
           <t>PROGRAMA DE GESTAO E MANUTENCAO DO PODER EXECUTIVO</t>
         </is>
@@ -907,7 +922,12 @@
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>Administração</t>
+          <t>overhead</t>
+        </is>
+      </c>
+      <c r="L9" t="inlineStr">
+        <is>
+          <t>model</t>
         </is>
       </c>
     </row>
@@ -962,10 +982,15 @@
       </c>
       <c r="K10" t="inlineStr">
         <is>
-          <t>Administração</t>
+          <t>development</t>
         </is>
       </c>
       <c r="L10" t="inlineStr">
+        <is>
+          <t>model</t>
+        </is>
+      </c>
+      <c r="N10" t="inlineStr">
         <is>
           <t>RECONSTRUCAO, AMPLIACAO E APROFUNDAMENTO DA PARTICIPACAO SOC</t>
         </is>
@@ -1022,10 +1047,15 @@
       </c>
       <c r="K11" t="inlineStr">
         <is>
-          <t>Administração</t>
+          <t>development</t>
         </is>
       </c>
       <c r="L11" t="inlineStr">
+        <is>
+          <t>model</t>
+        </is>
+      </c>
+      <c r="N11" t="inlineStr">
         <is>
           <t>PLANEJAMENTO E ORCAMENTO PARA O DESENVOLVIMENTO SUSTENTAVEL</t>
         </is>
@@ -1082,10 +1112,15 @@
       </c>
       <c r="K12" t="inlineStr">
         <is>
-          <t>Administração</t>
+          <t>development</t>
         </is>
       </c>
       <c r="L12" t="inlineStr">
+        <is>
+          <t>model</t>
+        </is>
+      </c>
+      <c r="N12" t="inlineStr">
         <is>
           <t>TRANSFORMACAO DO ESTADO PARA A CIDADANIA E O DESENVOLVIMENTO</t>
         </is>
@@ -1142,10 +1177,15 @@
       </c>
       <c r="K13" t="inlineStr">
         <is>
-          <t>Administração</t>
+          <t>development</t>
         </is>
       </c>
       <c r="L13" t="inlineStr">
+        <is>
+          <t>model</t>
+        </is>
+      </c>
+      <c r="N13" t="inlineStr">
         <is>
           <t>COMUNICACOES PARA INCLUSAO E TRANSFORMACAO</t>
         </is>
@@ -1202,10 +1242,15 @@
       </c>
       <c r="K14" t="inlineStr">
         <is>
-          <t>Administração</t>
+          <t>development</t>
         </is>
       </c>
       <c r="L14" t="inlineStr">
+        <is>
+          <t>model</t>
+        </is>
+      </c>
+      <c r="N14" t="inlineStr">
         <is>
           <t>POLITICA ECONOMICA PARA O CRESCIMENTO E DESENVOLVIMENTOSOCIO</t>
         </is>
@@ -1262,10 +1307,15 @@
       </c>
       <c r="K15" t="inlineStr">
         <is>
-          <t>Administração</t>
+          <t>development</t>
         </is>
       </c>
       <c r="L15" t="inlineStr">
+        <is>
+          <t>model</t>
+        </is>
+      </c>
+      <c r="N15" t="inlineStr">
         <is>
           <t>DESENVOLVIMENTO REGIONAL E ORDENAMENTO TERRITORIAL</t>
         </is>
@@ -1322,10 +1372,15 @@
       </c>
       <c r="K16" t="inlineStr">
         <is>
-          <t>Administração</t>
+          <t>development</t>
         </is>
       </c>
       <c r="L16" t="inlineStr">
+        <is>
+          <t>model</t>
+        </is>
+      </c>
+      <c r="N16" t="inlineStr">
         <is>
           <t>NEOINDUSTRIALIZACAO, AMBIENTE DE NEGOCIOS E PARTICIPACAO ECO</t>
         </is>
@@ -1382,7 +1437,12 @@
       </c>
       <c r="K17" t="inlineStr">
         <is>
-          <t>Administração</t>
+          <t>standing_function</t>
+        </is>
+      </c>
+      <c r="L17" t="inlineStr">
+        <is>
+          <t>model</t>
         </is>
       </c>
     </row>
@@ -1437,7 +1497,12 @@
       </c>
       <c r="K18" t="inlineStr">
         <is>
-          <t>Administração</t>
+          <t>standing_function</t>
+        </is>
+      </c>
+      <c r="L18" t="inlineStr">
+        <is>
+          <t>model</t>
         </is>
       </c>
     </row>
@@ -1492,10 +1557,15 @@
       </c>
       <c r="K19" t="inlineStr">
         <is>
-          <t>Administração</t>
+          <t>development</t>
         </is>
       </c>
       <c r="L19" t="inlineStr">
+        <is>
+          <t>model</t>
+        </is>
+      </c>
+      <c r="N19" t="inlineStr">
         <is>
           <t>SISTEMA FINANCEIRO DO FUTURO</t>
         </is>
@@ -1552,10 +1622,15 @@
       </c>
       <c r="K20" t="inlineStr">
         <is>
-          <t>Administração</t>
+          <t>development</t>
         </is>
       </c>
       <c r="L20" t="inlineStr">
+        <is>
+          <t>model</t>
+        </is>
+      </c>
+      <c r="N20" t="inlineStr">
         <is>
           <t>TRANSPARENCIA, INTEGRIDADE E ENFRENTAMENTO DA CORRUPCAO</t>
         </is>
@@ -1612,10 +1687,15 @@
       </c>
       <c r="K21" t="inlineStr">
         <is>
-          <t>Administração</t>
+          <t>standing_function</t>
         </is>
       </c>
       <c r="L21" t="inlineStr">
+        <is>
+          <t>model</t>
+        </is>
+      </c>
+      <c r="N21" t="inlineStr">
         <is>
           <t>EDUCACAO SUPERIOR: QUALIDADE, DEMOCRACIA, EQUIDADE E SUSTENT</t>
         </is>
@@ -1672,10 +1752,15 @@
       </c>
       <c r="K22" t="inlineStr">
         <is>
-          <t>Administração</t>
+          <t>development</t>
         </is>
       </c>
       <c r="L22" t="inlineStr">
+        <is>
+          <t>model</t>
+        </is>
+      </c>
+      <c r="N22" t="inlineStr">
         <is>
           <t>PROMOCAO DO ACESSO A JUSTICA E DA DEFESA DOS DIREITOS</t>
         </is>
@@ -1720,11 +1805,6 @@
           <t>/Users/sebastianpasha/Developer/Environment_UNDP/PV2/Files/llm/brazil/brazil_budget_2024.xlsx</t>
         </is>
       </c>
-      <c r="K23" t="inlineStr">
-        <is>
-          <t>Defesa nacional</t>
-        </is>
-      </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
@@ -1777,10 +1857,15 @@
       </c>
       <c r="K24" t="inlineStr">
         <is>
-          <t>Defesa nacional</t>
+          <t>standing_function</t>
         </is>
       </c>
       <c r="L24" t="inlineStr">
+        <is>
+          <t>model</t>
+        </is>
+      </c>
+      <c r="N24" t="inlineStr">
         <is>
           <t>PROGRAMA DE GESTAO E MANUTENCAO DO PODER EXECUTIVO</t>
         </is>
@@ -1837,10 +1922,15 @@
       </c>
       <c r="K25" t="inlineStr">
         <is>
-          <t>Defesa nacional</t>
+          <t>overhead</t>
         </is>
       </c>
       <c r="L25" t="inlineStr">
+        <is>
+          <t>model</t>
+        </is>
+      </c>
+      <c r="N25" t="inlineStr">
         <is>
           <t>OPERACOES ESPECIAIS: FINANCIAMENTOS COM RETORNO</t>
         </is>
@@ -1897,10 +1987,15 @@
       </c>
       <c r="K26" t="inlineStr">
         <is>
-          <t>Defesa nacional</t>
+          <t>development</t>
         </is>
       </c>
       <c r="L26" t="inlineStr">
+        <is>
+          <t>model</t>
+        </is>
+      </c>
+      <c r="N26" t="inlineStr">
         <is>
           <t>COOPERACAO DA DEFESA PARA O DESENVOLVIMENTO NACIONAL</t>
         </is>
@@ -1957,10 +2052,15 @@
       </c>
       <c r="K27" t="inlineStr">
         <is>
-          <t>Defesa nacional</t>
+          <t>standing_function</t>
         </is>
       </c>
       <c r="L27" t="inlineStr">
+        <is>
+          <t>model</t>
+        </is>
+      </c>
+      <c r="N27" t="inlineStr">
         <is>
           <t>DEFESA NACIONAL</t>
         </is>
@@ -2017,7 +2117,12 @@
       </c>
       <c r="K28" t="inlineStr">
         <is>
-          <t>Defesa nacional</t>
+          <t>development</t>
+        </is>
+      </c>
+      <c r="L28" t="inlineStr">
+        <is>
+          <t>model</t>
         </is>
       </c>
     </row>
@@ -2060,11 +2165,6 @@
           <t>/Users/sebastianpasha/Developer/Environment_UNDP/PV2/Files/llm/brazil/brazil_budget_2024.xlsx</t>
         </is>
       </c>
-      <c r="K29" t="inlineStr">
-        <is>
-          <t>Segurança pública</t>
-        </is>
-      </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
@@ -2117,10 +2217,15 @@
       </c>
       <c r="K30" t="inlineStr">
         <is>
-          <t>Segurança pública</t>
+          <t>standing_function</t>
         </is>
       </c>
       <c r="L30" t="inlineStr">
+        <is>
+          <t>model</t>
+        </is>
+      </c>
+      <c r="N30" t="inlineStr">
         <is>
           <t>PROGRAMA DE GESTAO E MANUTENCAO DO PODER EXECUTIVO</t>
         </is>
@@ -2177,10 +2282,15 @@
       </c>
       <c r="K31" t="inlineStr">
         <is>
-          <t>Segurança pública</t>
+          <t>development</t>
         </is>
       </c>
       <c r="L31" t="inlineStr">
+        <is>
+          <t>model</t>
+        </is>
+      </c>
+      <c r="N31" t="inlineStr">
         <is>
           <t>GESTAO DE RISCOS E DE DESASTRES</t>
         </is>
@@ -2237,10 +2347,15 @@
       </c>
       <c r="K32" t="inlineStr">
         <is>
-          <t>Segurança pública</t>
+          <t>development</t>
         </is>
       </c>
       <c r="L32" t="inlineStr">
+        <is>
+          <t>model</t>
+        </is>
+      </c>
+      <c r="N32" t="inlineStr">
         <is>
           <t>PROMOCAO DO ACESSO A JUSTICA E DA DEFESA DOS DIREITOS</t>
         </is>
@@ -2297,10 +2412,15 @@
       </c>
       <c r="K33" t="inlineStr">
         <is>
-          <t>Segurança pública</t>
+          <t>development</t>
         </is>
       </c>
       <c r="L33" t="inlineStr">
+        <is>
+          <t>model</t>
+        </is>
+      </c>
+      <c r="N33" t="inlineStr">
         <is>
           <t>SEGURANCA PUBLICA COM CIDADANIA</t>
         </is>
@@ -2345,11 +2465,6 @@
           <t>/Users/sebastianpasha/Developer/Environment_UNDP/PV2/Files/llm/brazil/brazil_budget_2024.xlsx</t>
         </is>
       </c>
-      <c r="K34" t="inlineStr">
-        <is>
-          <t>Relações exteriores</t>
-        </is>
-      </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
@@ -2402,10 +2517,15 @@
       </c>
       <c r="K35" t="inlineStr">
         <is>
-          <t>Relações exteriores</t>
+          <t>standing_function</t>
         </is>
       </c>
       <c r="L35" t="inlineStr">
+        <is>
+          <t>model</t>
+        </is>
+      </c>
+      <c r="N35" t="inlineStr">
         <is>
           <t>PROGRAMA DE GESTAO E MANUTENCAO DO PODER EXECUTIVO</t>
         </is>
@@ -2462,7 +2582,12 @@
       </c>
       <c r="K36" t="inlineStr">
         <is>
-          <t>Relações exteriores</t>
+          <t>overhead</t>
+        </is>
+      </c>
+      <c r="L36" t="inlineStr">
+        <is>
+          <t>model</t>
         </is>
       </c>
     </row>
@@ -2517,7 +2642,12 @@
       </c>
       <c r="K37" t="inlineStr">
         <is>
-          <t>Relações exteriores</t>
+          <t>standing_function</t>
+        </is>
+      </c>
+      <c r="L37" t="inlineStr">
+        <is>
+          <t>model</t>
         </is>
       </c>
     </row>
@@ -2560,11 +2690,6 @@
           <t>/Users/sebastianpasha/Developer/Environment_UNDP/PV2/Files/llm/brazil/brazil_budget_2024.xlsx</t>
         </is>
       </c>
-      <c r="K38" t="inlineStr">
-        <is>
-          <t>Assistência social</t>
-        </is>
-      </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
@@ -2617,10 +2742,15 @@
       </c>
       <c r="K39" t="inlineStr">
         <is>
-          <t>Assistência social</t>
+          <t>standing_function</t>
         </is>
       </c>
       <c r="L39" t="inlineStr">
+        <is>
+          <t>model</t>
+        </is>
+      </c>
+      <c r="N39" t="inlineStr">
         <is>
           <t>PROGRAMA DE GESTAO E MANUTENCAO DO PODER EXECUTIVO</t>
         </is>
@@ -2677,10 +2807,15 @@
       </c>
       <c r="K40" t="inlineStr">
         <is>
-          <t>Assistência social</t>
+          <t>development</t>
         </is>
       </c>
       <c r="L40" t="inlineStr">
+        <is>
+          <t>model</t>
+        </is>
+      </c>
+      <c r="N40" t="inlineStr">
         <is>
           <t>INCLUSAO SOCIOECONOMICA DO PUBLICO DO CADASTRO UNICO</t>
         </is>
@@ -2737,10 +2872,15 @@
       </c>
       <c r="K41" t="inlineStr">
         <is>
-          <t>Assistência social</t>
+          <t>standing_function</t>
         </is>
       </c>
       <c r="L41" t="inlineStr">
+        <is>
+          <t>model</t>
+        </is>
+      </c>
+      <c r="N41" t="inlineStr">
         <is>
           <t>BOLSA FAMILIA: PROTECAO SOCIAL POR MEIO DA TRANSFERENCIA DE</t>
         </is>
@@ -2797,10 +2937,15 @@
       </c>
       <c r="K42" t="inlineStr">
         <is>
-          <t>Assistência social</t>
+          <t>development</t>
         </is>
       </c>
       <c r="L42" t="inlineStr">
+        <is>
+          <t>model</t>
+        </is>
+      </c>
+      <c r="N42" t="inlineStr">
         <is>
           <t>INCLUSAO DE FAMILIAS EM SITUACAO DE VULNERABILIDADE NO CADAS</t>
         </is>
@@ -2857,10 +3002,15 @@
       </c>
       <c r="K43" t="inlineStr">
         <is>
-          <t>Assistência social</t>
+          <t>standing_function</t>
         </is>
       </c>
       <c r="L43" t="inlineStr">
+        <is>
+          <t>model</t>
+        </is>
+      </c>
+      <c r="N43" t="inlineStr">
         <is>
           <t>PROTECAO SOCIAL PELO SISTEMA UNICO DE ASSISTENCIA SOCIAL (SU</t>
         </is>
@@ -2917,7 +3067,12 @@
       </c>
       <c r="K44" t="inlineStr">
         <is>
-          <t>Assistência social</t>
+          <t>development</t>
+        </is>
+      </c>
+      <c r="L44" t="inlineStr">
+        <is>
+          <t>model</t>
         </is>
       </c>
     </row>
@@ -2972,10 +3127,15 @@
       </c>
       <c r="K45" t="inlineStr">
         <is>
-          <t>Assistência social</t>
+          <t>standing_function</t>
         </is>
       </c>
       <c r="L45" t="inlineStr">
+        <is>
+          <t>model</t>
+        </is>
+      </c>
+      <c r="N45" t="inlineStr">
         <is>
           <t>CUIDADO E ACOLHIMENTO DE USUARIOS E DEPENDENTES DE ALCOOL E</t>
         </is>
@@ -3032,10 +3192,15 @@
       </c>
       <c r="K46" t="inlineStr">
         <is>
-          <t>Assistência social</t>
+          <t>development</t>
         </is>
       </c>
       <c r="L46" t="inlineStr">
+        <is>
+          <t>model</t>
+        </is>
+      </c>
+      <c r="N46" t="inlineStr">
         <is>
           <t>ESTRUTURACAO DA POLITICA NACIONAL DE CUIDADOS</t>
         </is>
@@ -3092,10 +3257,15 @@
       </c>
       <c r="K47" t="inlineStr">
         <is>
-          <t>Assistência social</t>
+          <t>development</t>
         </is>
       </c>
       <c r="L47" t="inlineStr">
+        <is>
+          <t>model</t>
+        </is>
+      </c>
+      <c r="N47" t="inlineStr">
         <is>
           <t>PROMOCAO DOS DIREITOS DAS PESSOAS COM DEFICIENCIA</t>
         </is>
@@ -3140,11 +3310,6 @@
           <t>/Users/sebastianpasha/Developer/Environment_UNDP/PV2/Files/llm/brazil/brazil_budget_2024.xlsx</t>
         </is>
       </c>
-      <c r="K48" t="inlineStr">
-        <is>
-          <t>Previdência social</t>
-        </is>
-      </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
@@ -3197,10 +3362,15 @@
       </c>
       <c r="K49" t="inlineStr">
         <is>
-          <t>Previdência social</t>
+          <t>standing_function</t>
         </is>
       </c>
       <c r="L49" t="inlineStr">
+        <is>
+          <t>model</t>
+        </is>
+      </c>
+      <c r="N49" t="inlineStr">
         <is>
           <t>PROGRAMA DE GESTAO E MANUTENCAO DO PODER EXECUTIVO</t>
         </is>
@@ -3257,7 +3427,12 @@
       </c>
       <c r="K50" t="inlineStr">
         <is>
-          <t>Previdência social</t>
+          <t>overhead</t>
+        </is>
+      </c>
+      <c r="L50" t="inlineStr">
+        <is>
+          <t>model</t>
         </is>
       </c>
     </row>
@@ -3312,10 +3487,15 @@
       </c>
       <c r="K51" t="inlineStr">
         <is>
-          <t>Previdência social</t>
+          <t>standing_function</t>
         </is>
       </c>
       <c r="L51" t="inlineStr">
+        <is>
+          <t>model</t>
+        </is>
+      </c>
+      <c r="N51" t="inlineStr">
         <is>
           <t>PREVIDENCIA SOCIAL: PROMOCAO, GARANTIA DE DIREITOS E CIDADAN</t>
         </is>
@@ -3360,11 +3540,6 @@
           <t>/Users/sebastianpasha/Developer/Environment_UNDP/PV2/Files/llm/brazil/brazil_budget_2024.xlsx</t>
         </is>
       </c>
-      <c r="K52" t="inlineStr">
-        <is>
-          <t>Saúde</t>
-        </is>
-      </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
@@ -3417,10 +3592,15 @@
       </c>
       <c r="K53" t="inlineStr">
         <is>
-          <t>Saúde</t>
+          <t>standing_function</t>
         </is>
       </c>
       <c r="L53" t="inlineStr">
+        <is>
+          <t>model</t>
+        </is>
+      </c>
+      <c r="N53" t="inlineStr">
         <is>
           <t>PROGRAMA DE GESTAO E MANUTENCAO DO PODER EXECUTIVO</t>
         </is>
@@ -3477,10 +3657,15 @@
       </c>
       <c r="K54" t="inlineStr">
         <is>
-          <t>Saúde</t>
+          <t>overhead</t>
         </is>
       </c>
       <c r="L54" t="inlineStr">
+        <is>
+          <t>model</t>
+        </is>
+      </c>
+      <c r="N54" t="inlineStr">
         <is>
           <t>OPERACOES ESPECIAIS: GESTAO DA PARTICIPACAO EM ORGANISMOS E</t>
         </is>
@@ -3537,7 +3722,12 @@
       </c>
       <c r="K55" t="inlineStr">
         <is>
-          <t>Saúde</t>
+          <t>development</t>
+        </is>
+      </c>
+      <c r="L55" t="inlineStr">
+        <is>
+          <t>model</t>
         </is>
       </c>
     </row>
@@ -3592,10 +3782,15 @@
       </c>
       <c r="K56" t="inlineStr">
         <is>
-          <t>Saúde</t>
+          <t>standing_function</t>
         </is>
       </c>
       <c r="L56" t="inlineStr">
+        <is>
+          <t>model</t>
+        </is>
+      </c>
+      <c r="N56" t="inlineStr">
         <is>
           <t>QUALIFICACAO DA ASSISTENCIA FARMACEUTICA NO SISTEMA UNICO DE</t>
         </is>
@@ -3652,10 +3847,15 @@
       </c>
       <c r="K57" t="inlineStr">
         <is>
-          <t>Saúde</t>
+          <t>standing_function</t>
         </is>
       </c>
       <c r="L57" t="inlineStr">
+        <is>
+          <t>model</t>
+        </is>
+      </c>
+      <c r="N57" t="inlineStr">
         <is>
           <t>ATENCAO ESPECIALIZADA A SAUDE</t>
         </is>
@@ -3712,10 +3912,15 @@
       </c>
       <c r="K58" t="inlineStr">
         <is>
-          <t>Saúde</t>
+          <t>standing_function</t>
         </is>
       </c>
       <c r="L58" t="inlineStr">
+        <is>
+          <t>model</t>
+        </is>
+      </c>
+      <c r="N58" t="inlineStr">
         <is>
           <t>ATENCAO PRIMARIA A SAUDE</t>
         </is>
@@ -3772,10 +3977,15 @@
       </c>
       <c r="K59" t="inlineStr">
         <is>
-          <t>Saúde</t>
+          <t>development</t>
         </is>
       </c>
       <c r="L59" t="inlineStr">
+        <is>
+          <t>model</t>
+        </is>
+      </c>
+      <c r="N59" t="inlineStr">
         <is>
           <t>PESQUISA, DESENVOLVIMENTO, INOVACAO, PRODUCAO E AVALIACAO DE</t>
         </is>
@@ -3832,10 +4042,15 @@
       </c>
       <c r="K60" t="inlineStr">
         <is>
-          <t>Saúde</t>
+          <t>standing_function</t>
         </is>
       </c>
       <c r="L60" t="inlineStr">
+        <is>
+          <t>model</t>
+        </is>
+      </c>
+      <c r="N60" t="inlineStr">
         <is>
           <t>GESTAO, TRABALHO, EDUCACAO E TRANSFORMACAO DIGITAL NA SAUDE</t>
         </is>
@@ -3892,10 +4107,15 @@
       </c>
       <c r="K61" t="inlineStr">
         <is>
-          <t>Saúde</t>
+          <t>development</t>
         </is>
       </c>
       <c r="L61" t="inlineStr">
+        <is>
+          <t>model</t>
+        </is>
+      </c>
+      <c r="N61" t="inlineStr">
         <is>
           <t>SAUDE INDIGENA</t>
         </is>
@@ -3952,10 +4172,15 @@
       </c>
       <c r="K62" t="inlineStr">
         <is>
-          <t>Saúde</t>
+          <t>standing_function</t>
         </is>
       </c>
       <c r="L62" t="inlineStr">
+        <is>
+          <t>model</t>
+        </is>
+      </c>
+      <c r="N62" t="inlineStr">
         <is>
           <t>VIGILANCIA EM SAUDE E AMBIENTE</t>
         </is>
@@ -4012,7 +4237,12 @@
       </c>
       <c r="K63" t="inlineStr">
         <is>
-          <t>Saúde</t>
+          <t>development</t>
+        </is>
+      </c>
+      <c r="L63" t="inlineStr">
+        <is>
+          <t>model</t>
         </is>
       </c>
     </row>
@@ -4105,7 +4335,17 @@
           <t>/Users/sebastianpasha/Developer/Environment_UNDP/PV2/Files/llm/brazil/brazil_budget_2024.xlsx</t>
         </is>
       </c>
+      <c r="K65" t="inlineStr">
+        <is>
+          <t>standing_function</t>
+        </is>
+      </c>
       <c r="L65" t="inlineStr">
+        <is>
+          <t>model</t>
+        </is>
+      </c>
+      <c r="N65" t="inlineStr">
         <is>
           <t>PROGRAMA DE GESTAO E MANUTENCAO DO PODER EXECUTIVO</t>
         </is>
@@ -4160,7 +4400,17 @@
           <t>/Users/sebastianpasha/Developer/Environment_UNDP/PV2/Files/llm/brazil/brazil_budget_2024.xlsx</t>
         </is>
       </c>
+      <c r="K66" t="inlineStr">
+        <is>
+          <t>overhead</t>
+        </is>
+      </c>
       <c r="L66" t="inlineStr">
+        <is>
+          <t>model</t>
+        </is>
+      </c>
+      <c r="N66" t="inlineStr">
         <is>
           <t>OPERACOES ESPECIAIS: FINANCIAMENTOS COM RETORNO</t>
         </is>
@@ -4215,7 +4465,17 @@
           <t>/Users/sebastianpasha/Developer/Environment_UNDP/PV2/Files/llm/brazil/brazil_budget_2024.xlsx</t>
         </is>
       </c>
+      <c r="K67" t="inlineStr">
+        <is>
+          <t>development</t>
+        </is>
+      </c>
       <c r="L67" t="inlineStr">
+        <is>
+          <t>model</t>
+        </is>
+      </c>
+      <c r="N67" t="inlineStr">
         <is>
           <t>PROMOCAO DO TRABALHO DECENTE, EMPREGO E RENDA</t>
         </is>
@@ -4270,7 +4530,17 @@
           <t>/Users/sebastianpasha/Developer/Environment_UNDP/PV2/Files/llm/brazil/brazil_budget_2024.xlsx</t>
         </is>
       </c>
+      <c r="K68" t="inlineStr">
+        <is>
+          <t>development</t>
+        </is>
+      </c>
       <c r="L68" t="inlineStr">
+        <is>
+          <t>model</t>
+        </is>
+      </c>
+      <c r="N68" t="inlineStr">
         <is>
           <t>DESENVOLVIMENTO REGIONAL E ORDENAMENTO TERRITORIAL</t>
         </is>
@@ -4325,6 +4595,16 @@
           <t>/Users/sebastianpasha/Developer/Environment_UNDP/PV2/Files/llm/brazil/brazil_budget_2024.xlsx</t>
         </is>
       </c>
+      <c r="K69" t="inlineStr">
+        <is>
+          <t>development</t>
+        </is>
+      </c>
+      <c r="L69" t="inlineStr">
+        <is>
+          <t>model</t>
+        </is>
+      </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
@@ -4365,11 +4645,6 @@
           <t>/Users/sebastianpasha/Developer/Environment_UNDP/PV2/Files/llm/brazil/brazil_budget_2024.xlsx</t>
         </is>
       </c>
-      <c r="K70" t="inlineStr">
-        <is>
-          <t>Educação</t>
-        </is>
-      </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
@@ -4422,10 +4697,15 @@
       </c>
       <c r="K71" t="inlineStr">
         <is>
-          <t>Educação</t>
+          <t>standing_function</t>
         </is>
       </c>
       <c r="L71" t="inlineStr">
+        <is>
+          <t>model</t>
+        </is>
+      </c>
+      <c r="N71" t="inlineStr">
         <is>
           <t>PROGRAMA DE GESTAO E MANUTENCAO DO PODER EXECUTIVO</t>
         </is>
@@ -4482,10 +4762,15 @@
       </c>
       <c r="K72" t="inlineStr">
         <is>
-          <t>Educação</t>
+          <t>overhead</t>
         </is>
       </c>
       <c r="L72" t="inlineStr">
+        <is>
+          <t>model</t>
+        </is>
+      </c>
+      <c r="N72" t="inlineStr">
         <is>
           <t>OPERACOES ESPECIAIS: FINANCIAMENTOS COM RETORNO</t>
         </is>
@@ -4542,7 +4827,12 @@
       </c>
       <c r="K73" t="inlineStr">
         <is>
-          <t>Educação</t>
+          <t>overhead</t>
+        </is>
+      </c>
+      <c r="L73" t="inlineStr">
+        <is>
+          <t>model</t>
         </is>
       </c>
     </row>
@@ -4597,10 +4887,15 @@
       </c>
       <c r="K74" t="inlineStr">
         <is>
-          <t>Educação</t>
+          <t>standing_function</t>
         </is>
       </c>
       <c r="L74" t="inlineStr">
+        <is>
+          <t>model</t>
+        </is>
+      </c>
+      <c r="N74" t="inlineStr">
         <is>
           <t>EDUCACAO BASICA DEMOCRATICA, COM QUALIDADE E EQUIDADE</t>
         </is>
@@ -4657,10 +4952,15 @@
       </c>
       <c r="K75" t="inlineStr">
         <is>
-          <t>Educação</t>
+          <t>development</t>
         </is>
       </c>
       <c r="L75" t="inlineStr">
+        <is>
+          <t>model</t>
+        </is>
+      </c>
+      <c r="N75" t="inlineStr">
         <is>
           <t>EDUCACAO PROFISSIONAL E TECNOLOGICA QUE TRANSFORMA</t>
         </is>
@@ -4717,10 +5017,15 @@
       </c>
       <c r="K76" t="inlineStr">
         <is>
-          <t>Educação</t>
+          <t>standing_function</t>
         </is>
       </c>
       <c r="L76" t="inlineStr">
+        <is>
+          <t>model</t>
+        </is>
+      </c>
+      <c r="N76" t="inlineStr">
         <is>
           <t>EDUCACAO SUPERIOR: QUALIDADE, DEMOCRACIA, EQUIDADE E SUSTENT</t>
         </is>
@@ -4815,7 +5120,17 @@
           <t>/Users/sebastianpasha/Developer/Environment_UNDP/PV2/Files/llm/brazil/brazil_budget_2024.xlsx</t>
         </is>
       </c>
+      <c r="K78" t="inlineStr">
+        <is>
+          <t>standing_function</t>
+        </is>
+      </c>
       <c r="L78" t="inlineStr">
+        <is>
+          <t>model</t>
+        </is>
+      </c>
+      <c r="N78" t="inlineStr">
         <is>
           <t>PROGRAMA DE GESTAO E MANUTENCAO DO PODER EXECUTIVO</t>
         </is>
@@ -4870,6 +5185,16 @@
           <t>/Users/sebastianpasha/Developer/Environment_UNDP/PV2/Files/llm/brazil/brazil_budget_2024.xlsx</t>
         </is>
       </c>
+      <c r="K79" t="inlineStr">
+        <is>
+          <t>development</t>
+        </is>
+      </c>
+      <c r="L79" t="inlineStr">
+        <is>
+          <t>model</t>
+        </is>
+      </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
@@ -4910,11 +5235,6 @@
           <t>/Users/sebastianpasha/Developer/Environment_UNDP/PV2/Files/llm/brazil/brazil_budget_2024.xlsx</t>
         </is>
       </c>
-      <c r="K80" t="inlineStr">
-        <is>
-          <t>Direitos da cidadania</t>
-        </is>
-      </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
@@ -4967,10 +5287,15 @@
       </c>
       <c r="K81" t="inlineStr">
         <is>
-          <t>Direitos da cidadania</t>
+          <t>standing_function</t>
         </is>
       </c>
       <c r="L81" t="inlineStr">
+        <is>
+          <t>model</t>
+        </is>
+      </c>
+      <c r="N81" t="inlineStr">
         <is>
           <t>PROGRAMA DE GESTAO E MANUTENCAO DO PODER EXECUTIVO</t>
         </is>
@@ -5027,10 +5352,15 @@
       </c>
       <c r="K82" t="inlineStr">
         <is>
-          <t>Direitos da cidadania</t>
+          <t>development</t>
         </is>
       </c>
       <c r="L82" t="inlineStr">
+        <is>
+          <t>model</t>
+        </is>
+      </c>
+      <c r="N82" t="inlineStr">
         <is>
           <t>PROTECAO DE TERRAS INDIGENAS, GESTAO TERRITORIAL E ETNODESEN</t>
         </is>
@@ -5087,10 +5417,15 @@
       </c>
       <c r="K83" t="inlineStr">
         <is>
-          <t>Direitos da cidadania</t>
+          <t>overhead</t>
         </is>
       </c>
       <c r="L83" t="inlineStr">
+        <is>
+          <t>model</t>
+        </is>
+      </c>
+      <c r="N83" t="inlineStr">
         <is>
           <t>OPERACOES ESPECIAIS: GESTAO DA PARTICIPACAO EM ORGANISMOS E</t>
         </is>
@@ -5147,10 +5482,15 @@
       </c>
       <c r="K84" t="inlineStr">
         <is>
-          <t>Direitos da cidadania</t>
+          <t>development</t>
         </is>
       </c>
       <c r="L84" t="inlineStr">
+        <is>
+          <t>model</t>
+        </is>
+      </c>
+      <c r="N84" t="inlineStr">
         <is>
           <t>RECONSTRUCAO, AMPLIACAO E APROFUNDAMENTO DA PARTICIPACAO SOC</t>
         </is>
@@ -5207,10 +5547,15 @@
       </c>
       <c r="K85" t="inlineStr">
         <is>
-          <t>Direitos da cidadania</t>
+          <t>development</t>
         </is>
       </c>
       <c r="L85" t="inlineStr">
+        <is>
+          <t>model</t>
+        </is>
+      </c>
+      <c r="N85" t="inlineStr">
         <is>
           <t>DEMARCACAO E GESTAO DOS TERRITORIOS INDIGENAS PARA O BEM VIV</t>
         </is>
@@ -5267,10 +5612,15 @@
       </c>
       <c r="K86" t="inlineStr">
         <is>
-          <t>Direitos da cidadania</t>
+          <t>development</t>
         </is>
       </c>
       <c r="L86" t="inlineStr">
+        <is>
+          <t>model</t>
+        </is>
+      </c>
+      <c r="N86" t="inlineStr">
         <is>
           <t>PROMOCAO DO ACESSO A JUSTICA E DA DEFESA DOS DIREITOS</t>
         </is>
@@ -5327,10 +5677,15 @@
       </c>
       <c r="K87" t="inlineStr">
         <is>
-          <t>Direitos da cidadania</t>
+          <t>development</t>
         </is>
       </c>
       <c r="L87" t="inlineStr">
+        <is>
+          <t>model</t>
+        </is>
+      </c>
+      <c r="N87" t="inlineStr">
         <is>
           <t>SEGURANCA PUBLICA COM CIDADANIA</t>
         </is>
@@ -5387,10 +5742,15 @@
       </c>
       <c r="K88" t="inlineStr">
         <is>
-          <t>Direitos da cidadania</t>
+          <t>development</t>
         </is>
       </c>
       <c r="L88" t="inlineStr">
+        <is>
+          <t>model</t>
+        </is>
+      </c>
+      <c r="N88" t="inlineStr">
         <is>
           <t>JUVENTUDE: DIREITOS, PARTICIPACAO E BEM VIVER</t>
         </is>
@@ -5447,10 +5807,15 @@
       </c>
       <c r="K89" t="inlineStr">
         <is>
-          <t>Direitos da cidadania</t>
+          <t>development</t>
         </is>
       </c>
       <c r="L89" t="inlineStr">
+        <is>
+          <t>model</t>
+        </is>
+      </c>
+      <c r="N89" t="inlineStr">
         <is>
           <t>IGUALDADE DE DECISAO E PODER PARA MULHERES</t>
         </is>
@@ -5507,7 +5872,12 @@
       </c>
       <c r="K90" t="inlineStr">
         <is>
-          <t>Direitos da cidadania</t>
+          <t>development</t>
+        </is>
+      </c>
+      <c r="L90" t="inlineStr">
+        <is>
+          <t>model</t>
         </is>
       </c>
     </row>
@@ -5562,10 +5932,15 @@
       </c>
       <c r="K91" t="inlineStr">
         <is>
-          <t>Direitos da cidadania</t>
+          <t>development</t>
         </is>
       </c>
       <c r="L91" t="inlineStr">
+        <is>
+          <t>model</t>
+        </is>
+      </c>
+      <c r="N91" t="inlineStr">
         <is>
           <t>AUTONOMIA ECONOMICA DAS MULHERES</t>
         </is>
@@ -5622,10 +5997,15 @@
       </c>
       <c r="K92" t="inlineStr">
         <is>
-          <t>Direitos da cidadania</t>
+          <t>development</t>
         </is>
       </c>
       <c r="L92" t="inlineStr">
+        <is>
+          <t>model</t>
+        </is>
+      </c>
+      <c r="N92" t="inlineStr">
         <is>
           <t>POLITICAS PARA QUILOMBOLAS, COMUNIDADES TRADICIONAIS DEMATRI</t>
         </is>
@@ -5682,7 +6062,12 @@
       </c>
       <c r="K93" t="inlineStr">
         <is>
-          <t>Direitos da cidadania</t>
+          <t>development</t>
+        </is>
+      </c>
+      <c r="L93" t="inlineStr">
+        <is>
+          <t>model</t>
         </is>
       </c>
     </row>
@@ -5737,10 +6122,15 @@
       </c>
       <c r="K94" t="inlineStr">
         <is>
-          <t>Direitos da cidadania</t>
+          <t>development</t>
         </is>
       </c>
       <c r="L94" t="inlineStr">
+        <is>
+          <t>model</t>
+        </is>
+      </c>
+      <c r="N94" t="inlineStr">
         <is>
           <t>PROMOCAO DA IGUALDADE ETNICO-RACIAL, COMBATE E SUPERACAO DO</t>
         </is>
@@ -5797,10 +6187,15 @@
       </c>
       <c r="K95" t="inlineStr">
         <is>
-          <t>Direitos da cidadania</t>
+          <t>development</t>
         </is>
       </c>
       <c r="L95" t="inlineStr">
+        <is>
+          <t>model</t>
+        </is>
+      </c>
+      <c r="N95" t="inlineStr">
         <is>
           <t>PROMOCAO DOS DIREITOS DAS PESSOAS COM DEFICIENCIA</t>
         </is>
@@ -5857,10 +6252,15 @@
       </c>
       <c r="K96" t="inlineStr">
         <is>
-          <t>Direitos da cidadania</t>
+          <t>development</t>
         </is>
       </c>
       <c r="L96" t="inlineStr">
+        <is>
+          <t>model</t>
+        </is>
+      </c>
+      <c r="N96" t="inlineStr">
         <is>
           <t>PROMOCAO E DEFESA DOS DIREITOS DAS PESSOAS LGBTQIA+</t>
         </is>
@@ -5917,10 +6317,15 @@
       </c>
       <c r="K97" t="inlineStr">
         <is>
-          <t>Direitos da cidadania</t>
+          <t>development</t>
         </is>
       </c>
       <c r="L97" t="inlineStr">
+        <is>
+          <t>model</t>
+        </is>
+      </c>
+      <c r="N97" t="inlineStr">
         <is>
           <t>PROGRAMA NACIONAL DE PROMOCAO DOS DIREITOS DA POPULACAOEM SI</t>
         </is>
@@ -5977,10 +6382,15 @@
       </c>
       <c r="K98" t="inlineStr">
         <is>
-          <t>Direitos da cidadania</t>
+          <t>development</t>
         </is>
       </c>
       <c r="L98" t="inlineStr">
+        <is>
+          <t>model</t>
+        </is>
+      </c>
+      <c r="N98" t="inlineStr">
         <is>
           <t>PROMOCAO DO DIREITO DE ENVELHECER E DOS DIREITOS HUMANOS DA</t>
         </is>
@@ -6037,10 +6447,15 @@
       </c>
       <c r="K99" t="inlineStr">
         <is>
-          <t>Direitos da cidadania</t>
+          <t>development</t>
         </is>
       </c>
       <c r="L99" t="inlineStr">
+        <is>
+          <t>model</t>
+        </is>
+      </c>
+      <c r="N99" t="inlineStr">
         <is>
           <t>PROMOCAO E PROTECAO INTEGRAL DOS DIREITOS HUMANOS DE CRIANCA</t>
         </is>
@@ -6097,10 +6512,15 @@
       </c>
       <c r="K100" t="inlineStr">
         <is>
-          <t>Direitos da cidadania</t>
+          <t>development</t>
         </is>
       </c>
       <c r="L100" t="inlineStr">
+        <is>
+          <t>model</t>
+        </is>
+      </c>
+      <c r="N100" t="inlineStr">
         <is>
           <t>PROMOCAO DA CIDADANIA, DEFESA DE DIREITOS HUMANOS E REPARACA</t>
         </is>
@@ -6157,10 +6577,15 @@
       </c>
       <c r="K101" t="inlineStr">
         <is>
-          <t>Direitos da cidadania</t>
+          <t>development</t>
         </is>
       </c>
       <c r="L101" t="inlineStr">
+        <is>
+          <t>model</t>
+        </is>
+      </c>
+      <c r="N101" t="inlineStr">
         <is>
           <t>DIREITOS PLURIETNICOS CULTURAIS E SOCIAIS PARA O PLENO EXERC</t>
         </is>
@@ -6255,7 +6680,17 @@
           <t>/Users/sebastianpasha/Developer/Environment_UNDP/PV2/Files/llm/brazil/brazil_budget_2024.xlsx</t>
         </is>
       </c>
+      <c r="K103" t="inlineStr">
+        <is>
+          <t>standing_function</t>
+        </is>
+      </c>
       <c r="L103" t="inlineStr">
+        <is>
+          <t>model</t>
+        </is>
+      </c>
+      <c r="N103" t="inlineStr">
         <is>
           <t>PROGRAMA DE GESTAO E MANUTENCAO DO PODER EXECUTIVO</t>
         </is>
@@ -6310,7 +6745,17 @@
           <t>/Users/sebastianpasha/Developer/Environment_UNDP/PV2/Files/llm/brazil/brazil_budget_2024.xlsx</t>
         </is>
       </c>
+      <c r="K104" t="inlineStr">
+        <is>
+          <t>development</t>
+        </is>
+      </c>
       <c r="L104" t="inlineStr">
+        <is>
+          <t>model</t>
+        </is>
+      </c>
+      <c r="N104" t="inlineStr">
         <is>
           <t>DESENVOLVIMENTO REGIONAL E ORDENAMENTO TERRITORIAL</t>
         </is>
@@ -6365,7 +6810,17 @@
           <t>/Users/sebastianpasha/Developer/Environment_UNDP/PV2/Files/llm/brazil/brazil_budget_2024.xlsx</t>
         </is>
       </c>
+      <c r="K105" t="inlineStr">
+        <is>
+          <t>development</t>
+        </is>
+      </c>
       <c r="L105" t="inlineStr">
+        <is>
+          <t>model</t>
+        </is>
+      </c>
+      <c r="N105" t="inlineStr">
         <is>
           <t>GESTAO DE RISCOS E DE DESASTRES</t>
         </is>
@@ -6420,6 +6875,16 @@
           <t>/Users/sebastianpasha/Developer/Environment_UNDP/PV2/Files/llm/brazil/brazil_budget_2024.xlsx</t>
         </is>
       </c>
+      <c r="K106" t="inlineStr">
+        <is>
+          <t>development</t>
+        </is>
+      </c>
+      <c r="L106" t="inlineStr">
+        <is>
+          <t>model</t>
+        </is>
+      </c>
     </row>
     <row r="107">
       <c r="A107" t="inlineStr">
@@ -6470,6 +6935,16 @@
           <t>/Users/sebastianpasha/Developer/Environment_UNDP/PV2/Files/llm/brazil/brazil_budget_2024.xlsx</t>
         </is>
       </c>
+      <c r="K107" t="inlineStr">
+        <is>
+          <t>development</t>
+        </is>
+      </c>
+      <c r="L107" t="inlineStr">
+        <is>
+          <t>model</t>
+        </is>
+      </c>
     </row>
     <row r="108">
       <c r="A108" t="inlineStr">
@@ -6520,6 +6995,16 @@
           <t>/Users/sebastianpasha/Developer/Environment_UNDP/PV2/Files/llm/brazil/brazil_budget_2024.xlsx</t>
         </is>
       </c>
+      <c r="K108" t="inlineStr">
+        <is>
+          <t>development</t>
+        </is>
+      </c>
+      <c r="L108" t="inlineStr">
+        <is>
+          <t>model</t>
+        </is>
+      </c>
     </row>
     <row r="109">
       <c r="A109" t="inlineStr">
@@ -6570,6 +7055,16 @@
           <t>/Users/sebastianpasha/Developer/Environment_UNDP/PV2/Files/llm/brazil/brazil_budget_2024.xlsx</t>
         </is>
       </c>
+      <c r="K109" t="inlineStr">
+        <is>
+          <t>development</t>
+        </is>
+      </c>
+      <c r="L109" t="inlineStr">
+        <is>
+          <t>model</t>
+        </is>
+      </c>
     </row>
     <row r="110">
       <c r="A110" t="inlineStr">
@@ -6610,11 +7105,6 @@
           <t>/Users/sebastianpasha/Developer/Environment_UNDP/PV2/Files/llm/brazil/brazil_budget_2024.xlsx</t>
         </is>
       </c>
-      <c r="K110" t="inlineStr">
-        <is>
-          <t>Habitação</t>
-        </is>
-      </c>
     </row>
     <row r="111">
       <c r="A111" t="inlineStr">
@@ -6667,7 +7157,12 @@
       </c>
       <c r="K111" t="inlineStr">
         <is>
-          <t>Habitação</t>
+          <t>development</t>
+        </is>
+      </c>
+      <c r="L111" t="inlineStr">
+        <is>
+          <t>model</t>
         </is>
       </c>
     </row>
@@ -6722,7 +7217,12 @@
       </c>
       <c r="K112" t="inlineStr">
         <is>
-          <t>Habitação</t>
+          <t>development</t>
+        </is>
+      </c>
+      <c r="L112" t="inlineStr">
+        <is>
+          <t>model</t>
         </is>
       </c>
     </row>
@@ -6815,7 +7315,17 @@
           <t>/Users/sebastianpasha/Developer/Environment_UNDP/PV2/Files/llm/brazil/brazil_budget_2024.xlsx</t>
         </is>
       </c>
+      <c r="K114" t="inlineStr">
+        <is>
+          <t>development</t>
+        </is>
+      </c>
       <c r="L114" t="inlineStr">
+        <is>
+          <t>model</t>
+        </is>
+      </c>
+      <c r="N114" t="inlineStr">
         <is>
           <t>GESTAO DE RISCOS E DE DESASTRES</t>
         </is>
@@ -6870,7 +7380,17 @@
           <t>/Users/sebastianpasha/Developer/Environment_UNDP/PV2/Files/llm/brazil/brazil_budget_2024.xlsx</t>
         </is>
       </c>
+      <c r="K115" t="inlineStr">
+        <is>
+          <t>development</t>
+        </is>
+      </c>
       <c r="L115" t="inlineStr">
+        <is>
+          <t>model</t>
+        </is>
+      </c>
+      <c r="N115" t="inlineStr">
         <is>
           <t>RECURSOS HIDRICOS: AGUA EM QUANTIDADE E QUALIDADE PARA SEMPR</t>
         </is>
@@ -6925,6 +7445,16 @@
           <t>/Users/sebastianpasha/Developer/Environment_UNDP/PV2/Files/llm/brazil/brazil_budget_2024.xlsx</t>
         </is>
       </c>
+      <c r="K116" t="inlineStr">
+        <is>
+          <t>development</t>
+        </is>
+      </c>
+      <c r="L116" t="inlineStr">
+        <is>
+          <t>model</t>
+        </is>
+      </c>
     </row>
     <row r="117">
       <c r="A117" t="inlineStr">
@@ -6965,11 +7495,6 @@
           <t>/Users/sebastianpasha/Developer/Environment_UNDP/PV2/Files/llm/brazil/brazil_budget_2024.xlsx</t>
         </is>
       </c>
-      <c r="K117" t="inlineStr">
-        <is>
-          <t>Gestão ambiental</t>
-        </is>
-      </c>
     </row>
     <row r="118">
       <c r="A118" t="inlineStr">
@@ -7022,10 +7547,15 @@
       </c>
       <c r="K118" t="inlineStr">
         <is>
-          <t>Gestão ambiental</t>
+          <t>standing_function</t>
         </is>
       </c>
       <c r="L118" t="inlineStr">
+        <is>
+          <t>model</t>
+        </is>
+      </c>
+      <c r="N118" t="inlineStr">
         <is>
           <t>PROGRAMA DE GESTAO E MANUTENCAO DO PODER EXECUTIVO</t>
         </is>
@@ -7082,10 +7612,15 @@
       </c>
       <c r="K119" t="inlineStr">
         <is>
-          <t>Gestão ambiental</t>
+          <t>development</t>
         </is>
       </c>
       <c r="L119" t="inlineStr">
+        <is>
+          <t>model</t>
+        </is>
+      </c>
+      <c r="N119" t="inlineStr">
         <is>
           <t>ENFRENTAMENTO DA EMERGENCIA CLIMATICA</t>
         </is>
@@ -7142,10 +7677,15 @@
       </c>
       <c r="K120" t="inlineStr">
         <is>
-          <t>Gestão ambiental</t>
+          <t>development</t>
         </is>
       </c>
       <c r="L120" t="inlineStr">
+        <is>
+          <t>model</t>
+        </is>
+      </c>
+      <c r="N120" t="inlineStr">
         <is>
           <t>BIOECONOMIA PARA UM NOVO CICLO DE PROSPERIDADE</t>
         </is>
@@ -7202,7 +7742,12 @@
       </c>
       <c r="K121" t="inlineStr">
         <is>
-          <t>Gestão ambiental</t>
+          <t>development</t>
+        </is>
+      </c>
+      <c r="L121" t="inlineStr">
+        <is>
+          <t>model</t>
         </is>
       </c>
     </row>
@@ -7257,10 +7802,15 @@
       </c>
       <c r="K122" t="inlineStr">
         <is>
-          <t>Gestão ambiental</t>
+          <t>development</t>
         </is>
       </c>
       <c r="L122" t="inlineStr">
+        <is>
+          <t>model</t>
+        </is>
+      </c>
+      <c r="N122" t="inlineStr">
         <is>
           <t>GESTAO DE RISCOS E DE DESASTRES</t>
         </is>
@@ -7317,10 +7867,15 @@
       </c>
       <c r="K123" t="inlineStr">
         <is>
-          <t>Gestão ambiental</t>
+          <t>development</t>
         </is>
       </c>
       <c r="L123" t="inlineStr">
+        <is>
+          <t>model</t>
+        </is>
+      </c>
+      <c r="N123" t="inlineStr">
         <is>
           <t>RECURSOS HIDRICOS: AGUA EM QUANTIDADE E QUALIDADE PARA SEMPR</t>
         </is>
@@ -7377,7 +7932,12 @@
       </c>
       <c r="K124" t="inlineStr">
         <is>
-          <t>Gestão ambiental</t>
+          <t>development</t>
+        </is>
+      </c>
+      <c r="L124" t="inlineStr">
+        <is>
+          <t>model</t>
         </is>
       </c>
     </row>
@@ -7432,10 +7992,15 @@
       </c>
       <c r="K125" t="inlineStr">
         <is>
-          <t>Gestão ambiental</t>
+          <t>standing_function</t>
         </is>
       </c>
       <c r="L125" t="inlineStr">
+        <is>
+          <t>model</t>
+        </is>
+      </c>
+      <c r="N125" t="inlineStr">
         <is>
           <t>EDUCACAO SUPERIOR: QUALIDADE, DEMOCRACIA, EQUIDADE E SUSTENT</t>
         </is>
@@ -7492,10 +8057,15 @@
       </c>
       <c r="K126" t="inlineStr">
         <is>
-          <t>Gestão ambiental</t>
+          <t>development</t>
         </is>
       </c>
       <c r="L126" t="inlineStr">
+        <is>
+          <t>model</t>
+        </is>
+      </c>
+      <c r="N126" t="inlineStr">
         <is>
           <t>PROTECAO E RECUPERACAO DA BIODIVERSIDADE E COMBATE AO DESMAT</t>
         </is>
@@ -7540,11 +8110,6 @@
           <t>/Users/sebastianpasha/Developer/Environment_UNDP/PV2/Files/llm/brazil/brazil_budget_2024.xlsx</t>
         </is>
       </c>
-      <c r="K127" t="inlineStr">
-        <is>
-          <t>Ciência e Tecnologia</t>
-        </is>
-      </c>
     </row>
     <row r="128">
       <c r="A128" t="inlineStr">
@@ -7597,10 +8162,15 @@
       </c>
       <c r="K128" t="inlineStr">
         <is>
-          <t>Ciência e Tecnologia</t>
+          <t>standing_function</t>
         </is>
       </c>
       <c r="L128" t="inlineStr">
+        <is>
+          <t>model</t>
+        </is>
+      </c>
+      <c r="N128" t="inlineStr">
         <is>
           <t>PROGRAMA DE GESTAO E MANUTENCAO DO PODER EXECUTIVO</t>
         </is>
@@ -7657,10 +8227,15 @@
       </c>
       <c r="K129" t="inlineStr">
         <is>
-          <t>Ciência e Tecnologia</t>
+          <t>overhead</t>
         </is>
       </c>
       <c r="L129" t="inlineStr">
+        <is>
+          <t>model</t>
+        </is>
+      </c>
+      <c r="N129" t="inlineStr">
         <is>
           <t>OPERACOES ESPECIAIS: FINANCIAMENTOS COM RETORNO</t>
         </is>
@@ -7717,7 +8292,12 @@
       </c>
       <c r="K130" t="inlineStr">
         <is>
-          <t>Ciência e Tecnologia</t>
+          <t>overhead</t>
+        </is>
+      </c>
+      <c r="L130" t="inlineStr">
+        <is>
+          <t>model</t>
         </is>
       </c>
     </row>
@@ -7772,10 +8352,15 @@
       </c>
       <c r="K131" t="inlineStr">
         <is>
-          <t>Ciência e Tecnologia</t>
+          <t>development</t>
         </is>
       </c>
       <c r="L131" t="inlineStr">
+        <is>
+          <t>model</t>
+        </is>
+      </c>
+      <c r="N131" t="inlineStr">
         <is>
           <t>ENFRENTAMENTO DA EMERGENCIA CLIMATICA</t>
         </is>
@@ -7832,10 +8417,15 @@
       </c>
       <c r="K132" t="inlineStr">
         <is>
-          <t>Ciência e Tecnologia</t>
+          <t>development</t>
         </is>
       </c>
       <c r="L132" t="inlineStr">
+        <is>
+          <t>model</t>
+        </is>
+      </c>
+      <c r="N132" t="inlineStr">
         <is>
           <t>CIENCIA, TECNOLOGIA E INOVACAO PARA O DESENVOLVIMENTO SOCIAL</t>
         </is>
@@ -7892,7 +8482,12 @@
       </c>
       <c r="K133" t="inlineStr">
         <is>
-          <t>Ciência e Tecnologia</t>
+          <t>development</t>
+        </is>
+      </c>
+      <c r="L133" t="inlineStr">
+        <is>
+          <t>model</t>
         </is>
       </c>
     </row>
@@ -7947,10 +8542,15 @@
       </c>
       <c r="K134" t="inlineStr">
         <is>
-          <t>Ciência e Tecnologia</t>
+          <t>development</t>
         </is>
       </c>
       <c r="L134" t="inlineStr">
+        <is>
+          <t>model</t>
+        </is>
+      </c>
+      <c r="N134" t="inlineStr">
         <is>
           <t>PROGRAMA ESPACIAL BRASILEIRO</t>
         </is>
@@ -8007,10 +8607,15 @@
       </c>
       <c r="K135" t="inlineStr">
         <is>
-          <t>Ciência e Tecnologia</t>
+          <t>development</t>
         </is>
       </c>
       <c r="L135" t="inlineStr">
+        <is>
+          <t>model</t>
+        </is>
+      </c>
+      <c r="N135" t="inlineStr">
         <is>
           <t>CONSOLIDACAO DO SISTEMA NACIONAL DE CIENCIA, TECNOLOGIAE INO</t>
         </is>
@@ -8067,10 +8672,15 @@
       </c>
       <c r="K136" t="inlineStr">
         <is>
-          <t>Ciência e Tecnologia</t>
+          <t>development</t>
         </is>
       </c>
       <c r="L136" t="inlineStr">
+        <is>
+          <t>model</t>
+        </is>
+      </c>
+      <c r="N136" t="inlineStr">
         <is>
           <t>DESENVOLVIMENTO REGIONAL E ORDENAMENTO TERRITORIAL</t>
         </is>
@@ -8127,10 +8737,15 @@
       </c>
       <c r="K137" t="inlineStr">
         <is>
-          <t>Ciência e Tecnologia</t>
+          <t>development</t>
         </is>
       </c>
       <c r="L137" t="inlineStr">
+        <is>
+          <t>model</t>
+        </is>
+      </c>
+      <c r="N137" t="inlineStr">
         <is>
           <t>GESTAO DE RISCOS E DE DESASTRES</t>
         </is>
@@ -8187,10 +8802,15 @@
       </c>
       <c r="K138" t="inlineStr">
         <is>
-          <t>Ciência e Tecnologia</t>
+          <t>development</t>
         </is>
       </c>
       <c r="L138" t="inlineStr">
+        <is>
+          <t>model</t>
+        </is>
+      </c>
+      <c r="N138" t="inlineStr">
         <is>
           <t>INOVACAO NAS EMPRESAS PARA UMA NOVA INDUSTRIALIZACAO</t>
         </is>
@@ -8247,7 +8867,12 @@
       </c>
       <c r="K139" t="inlineStr">
         <is>
-          <t>Ciência e Tecnologia</t>
+          <t>development</t>
+        </is>
+      </c>
+      <c r="L139" t="inlineStr">
+        <is>
+          <t>model</t>
         </is>
       </c>
     </row>
@@ -8302,10 +8927,15 @@
       </c>
       <c r="K140" t="inlineStr">
         <is>
-          <t>Ciência e Tecnologia</t>
+          <t>development</t>
         </is>
       </c>
       <c r="L140" t="inlineStr">
+        <is>
+          <t>model</t>
+        </is>
+      </c>
+      <c r="N140" t="inlineStr">
         <is>
           <t>PROTECAO E RECUPERACAO DA BIODIVERSIDADE E COMBATE AO DESMAT</t>
         </is>
@@ -8400,7 +9030,17 @@
           <t>/Users/sebastianpasha/Developer/Environment_UNDP/PV2/Files/llm/brazil/brazil_budget_2024.xlsx</t>
         </is>
       </c>
+      <c r="K142" t="inlineStr">
+        <is>
+          <t>standing_function</t>
+        </is>
+      </c>
       <c r="L142" t="inlineStr">
+        <is>
+          <t>model</t>
+        </is>
+      </c>
+      <c r="N142" t="inlineStr">
         <is>
           <t>PROGRAMA DE GESTAO E MANUTENCAO DO PODER EXECUTIVO</t>
         </is>
@@ -8455,7 +9095,17 @@
           <t>/Users/sebastianpasha/Developer/Environment_UNDP/PV2/Files/llm/brazil/brazil_budget_2024.xlsx</t>
         </is>
       </c>
+      <c r="K143" t="inlineStr">
+        <is>
+          <t>overhead</t>
+        </is>
+      </c>
       <c r="L143" t="inlineStr">
+        <is>
+          <t>model</t>
+        </is>
+      </c>
+      <c r="N143" t="inlineStr">
         <is>
           <t>OPERACOES ESPECIAIS: FINANCIAMENTOS COM RETORNO</t>
         </is>
@@ -8510,6 +9160,16 @@
           <t>/Users/sebastianpasha/Developer/Environment_UNDP/PV2/Files/llm/brazil/brazil_budget_2024.xlsx</t>
         </is>
       </c>
+      <c r="K144" t="inlineStr">
+        <is>
+          <t>development</t>
+        </is>
+      </c>
+      <c r="L144" t="inlineStr">
+        <is>
+          <t>model</t>
+        </is>
+      </c>
     </row>
     <row r="145">
       <c r="A145" t="inlineStr">
@@ -8560,6 +9220,16 @@
           <t>/Users/sebastianpasha/Developer/Environment_UNDP/PV2/Files/llm/brazil/brazil_budget_2024.xlsx</t>
         </is>
       </c>
+      <c r="K145" t="inlineStr">
+        <is>
+          <t>development</t>
+        </is>
+      </c>
+      <c r="L145" t="inlineStr">
+        <is>
+          <t>model</t>
+        </is>
+      </c>
     </row>
     <row r="146">
       <c r="A146" t="inlineStr">
@@ -8610,6 +9280,16 @@
           <t>/Users/sebastianpasha/Developer/Environment_UNDP/PV2/Files/llm/brazil/brazil_budget_2024.xlsx</t>
         </is>
       </c>
+      <c r="K146" t="inlineStr">
+        <is>
+          <t>standing_function</t>
+        </is>
+      </c>
+      <c r="L146" t="inlineStr">
+        <is>
+          <t>model</t>
+        </is>
+      </c>
     </row>
     <row r="147">
       <c r="A147" t="inlineStr">
@@ -8660,6 +9340,16 @@
           <t>/Users/sebastianpasha/Developer/Environment_UNDP/PV2/Files/llm/brazil/brazil_budget_2024.xlsx</t>
         </is>
       </c>
+      <c r="K147" t="inlineStr">
+        <is>
+          <t>development</t>
+        </is>
+      </c>
+      <c r="L147" t="inlineStr">
+        <is>
+          <t>model</t>
+        </is>
+      </c>
     </row>
     <row r="148">
       <c r="A148" t="inlineStr">
@@ -8710,7 +9400,17 @@
           <t>/Users/sebastianpasha/Developer/Environment_UNDP/PV2/Files/llm/brazil/brazil_budget_2024.xlsx</t>
         </is>
       </c>
+      <c r="K148" t="inlineStr">
+        <is>
+          <t>development</t>
+        </is>
+      </c>
       <c r="L148" t="inlineStr">
+        <is>
+          <t>model</t>
+        </is>
+      </c>
+      <c r="N148" t="inlineStr">
         <is>
           <t>DESENVOLVIMENTO REGIONAL E ORDENAMENTO TERRITORIAL</t>
         </is>
@@ -8765,7 +9465,17 @@
           <t>/Users/sebastianpasha/Developer/Environment_UNDP/PV2/Files/llm/brazil/brazil_budget_2024.xlsx</t>
         </is>
       </c>
+      <c r="K149" t="inlineStr">
+        <is>
+          <t>development</t>
+        </is>
+      </c>
       <c r="L149" t="inlineStr">
+        <is>
+          <t>model</t>
+        </is>
+      </c>
+      <c r="N149" t="inlineStr">
         <is>
           <t>RECURSOS HIDRICOS: AGUA EM QUANTIDADE E QUALIDADE PARA SEMPR</t>
         </is>
@@ -8820,6 +9530,16 @@
           <t>/Users/sebastianpasha/Developer/Environment_UNDP/PV2/Files/llm/brazil/brazil_budget_2024.xlsx</t>
         </is>
       </c>
+      <c r="K150" t="inlineStr">
+        <is>
+          <t>development</t>
+        </is>
+      </c>
+      <c r="L150" t="inlineStr">
+        <is>
+          <t>model</t>
+        </is>
+      </c>
     </row>
     <row r="151">
       <c r="A151" t="inlineStr">
@@ -8870,6 +9590,16 @@
           <t>/Users/sebastianpasha/Developer/Environment_UNDP/PV2/Files/llm/brazil/brazil_budget_2024.xlsx</t>
         </is>
       </c>
+      <c r="K151" t="inlineStr">
+        <is>
+          <t>development</t>
+        </is>
+      </c>
+      <c r="L151" t="inlineStr">
+        <is>
+          <t>model</t>
+        </is>
+      </c>
     </row>
     <row r="152">
       <c r="A152" t="inlineStr">
@@ -8910,11 +9640,6 @@
           <t>/Users/sebastianpasha/Developer/Environment_UNDP/PV2/Files/llm/brazil/brazil_budget_2024.xlsx</t>
         </is>
       </c>
-      <c r="K152" t="inlineStr">
-        <is>
-          <t>Organização agrária</t>
-        </is>
-      </c>
     </row>
     <row r="153">
       <c r="A153" t="inlineStr">
@@ -8967,10 +9692,15 @@
       </c>
       <c r="K153" t="inlineStr">
         <is>
-          <t>Organização agrária</t>
+          <t>standing_function</t>
         </is>
       </c>
       <c r="L153" t="inlineStr">
+        <is>
+          <t>model</t>
+        </is>
+      </c>
+      <c r="N153" t="inlineStr">
         <is>
           <t>PROGRAMA DE GESTAO E MANUTENCAO DO PODER EXECUTIVO</t>
         </is>
@@ -9027,7 +9757,12 @@
       </c>
       <c r="K154" t="inlineStr">
         <is>
-          <t>Organização agrária</t>
+          <t>development</t>
+        </is>
+      </c>
+      <c r="L154" t="inlineStr">
+        <is>
+          <t>model</t>
         </is>
       </c>
     </row>
@@ -9082,10 +9817,15 @@
       </c>
       <c r="K155" t="inlineStr">
         <is>
-          <t>Organização agrária</t>
+          <t>development</t>
         </is>
       </c>
       <c r="L155" t="inlineStr">
+        <is>
+          <t>model</t>
+        </is>
+      </c>
+      <c r="N155" t="inlineStr">
         <is>
           <t>GOVERNANCA FUNDIARIA, REFORMA AGRARIA E REGULARIZACAO DE TER</t>
         </is>
@@ -9142,7 +9882,12 @@
       </c>
       <c r="K156" t="inlineStr">
         <is>
-          <t>Organização agrária</t>
+          <t>development</t>
+        </is>
+      </c>
+      <c r="L156" t="inlineStr">
+        <is>
+          <t>model</t>
         </is>
       </c>
     </row>
@@ -9185,11 +9930,6 @@
           <t>/Users/sebastianpasha/Developer/Environment_UNDP/PV2/Files/llm/brazil/brazil_budget_2024.xlsx</t>
         </is>
       </c>
-      <c r="K157" t="inlineStr">
-        <is>
-          <t>Indústria</t>
-        </is>
-      </c>
     </row>
     <row r="158">
       <c r="A158" t="inlineStr">
@@ -9242,10 +9982,15 @@
       </c>
       <c r="K158" t="inlineStr">
         <is>
-          <t>Indústria</t>
+          <t>standing_function</t>
         </is>
       </c>
       <c r="L158" t="inlineStr">
+        <is>
+          <t>model</t>
+        </is>
+      </c>
+      <c r="N158" t="inlineStr">
         <is>
           <t>PROGRAMA DE GESTAO E MANUTENCAO DO PODER EXECUTIVO</t>
         </is>
@@ -9302,10 +10047,15 @@
       </c>
       <c r="K159" t="inlineStr">
         <is>
-          <t>Indústria</t>
+          <t>development</t>
         </is>
       </c>
       <c r="L159" t="inlineStr">
+        <is>
+          <t>model</t>
+        </is>
+      </c>
+      <c r="N159" t="inlineStr">
         <is>
           <t>GESTAO DE RISCOS E DE DESASTRES</t>
         </is>
@@ -9362,10 +10112,15 @@
       </c>
       <c r="K160" t="inlineStr">
         <is>
-          <t>Indústria</t>
+          <t>development</t>
         </is>
       </c>
       <c r="L160" t="inlineStr">
+        <is>
+          <t>model</t>
+        </is>
+      </c>
+      <c r="N160" t="inlineStr">
         <is>
           <t>RECURSOS HIDRICOS: AGUA EM QUANTIDADE E QUALIDADE PARA SEMPR</t>
         </is>
@@ -9422,10 +10177,15 @@
       </c>
       <c r="K161" t="inlineStr">
         <is>
-          <t>Indústria</t>
+          <t>development</t>
         </is>
       </c>
       <c r="L161" t="inlineStr">
+        <is>
+          <t>model</t>
+        </is>
+      </c>
+      <c r="N161" t="inlineStr">
         <is>
           <t>NEOINDUSTRIALIZACAO, AMBIENTE DE NEGOCIOS E PARTICIPACAO ECO</t>
         </is>
@@ -9482,7 +10242,12 @@
       </c>
       <c r="K162" t="inlineStr">
         <is>
-          <t>Indústria</t>
+          <t>development</t>
+        </is>
+      </c>
+      <c r="L162" t="inlineStr">
+        <is>
+          <t>model</t>
         </is>
       </c>
     </row>
@@ -9537,7 +10302,12 @@
       </c>
       <c r="K163" t="inlineStr">
         <is>
-          <t>Indústria</t>
+          <t>development</t>
+        </is>
+      </c>
+      <c r="L163" t="inlineStr">
+        <is>
+          <t>model</t>
         </is>
       </c>
     </row>
@@ -9580,11 +10350,6 @@
           <t>/Users/sebastianpasha/Developer/Environment_UNDP/PV2/Files/llm/brazil/brazil_budget_2024.xlsx</t>
         </is>
       </c>
-      <c r="K164" t="inlineStr">
-        <is>
-          <t>Comércio e serviços</t>
-        </is>
-      </c>
     </row>
     <row r="165">
       <c r="A165" t="inlineStr">
@@ -9637,10 +10402,15 @@
       </c>
       <c r="K165" t="inlineStr">
         <is>
-          <t>Comércio e serviços</t>
+          <t>standing_function</t>
         </is>
       </c>
       <c r="L165" t="inlineStr">
+        <is>
+          <t>model</t>
+        </is>
+      </c>
+      <c r="N165" t="inlineStr">
         <is>
           <t>PROGRAMA DE GESTAO E MANUTENCAO DO PODER EXECUTIVO</t>
         </is>
@@ -9697,10 +10467,15 @@
       </c>
       <c r="K166" t="inlineStr">
         <is>
-          <t>Comércio e serviços</t>
+          <t>overhead</t>
         </is>
       </c>
       <c r="L166" t="inlineStr">
+        <is>
+          <t>model</t>
+        </is>
+      </c>
+      <c r="N166" t="inlineStr">
         <is>
           <t>OPERACOES ESPECIAIS: FINANCIAMENTOS COM RETORNO</t>
         </is>
@@ -9757,7 +10532,12 @@
       </c>
       <c r="K167" t="inlineStr">
         <is>
-          <t>Comércio e serviços</t>
+          <t>overhead</t>
+        </is>
+      </c>
+      <c r="L167" t="inlineStr">
+        <is>
+          <t>model</t>
         </is>
       </c>
     </row>
@@ -9812,7 +10592,12 @@
       </c>
       <c r="K168" t="inlineStr">
         <is>
-          <t>Comércio e serviços</t>
+          <t>development</t>
+        </is>
+      </c>
+      <c r="L168" t="inlineStr">
+        <is>
+          <t>model</t>
         </is>
       </c>
     </row>
@@ -9867,10 +10652,15 @@
       </c>
       <c r="K169" t="inlineStr">
         <is>
-          <t>Comércio e serviços</t>
+          <t>development</t>
         </is>
       </c>
       <c r="L169" t="inlineStr">
+        <is>
+          <t>model</t>
+        </is>
+      </c>
+      <c r="N169" t="inlineStr">
         <is>
           <t>NEOINDUSTRIALIZACAO, AMBIENTE DE NEGOCIOS E PARTICIPACAO ECO</t>
         </is>
@@ -9915,11 +10705,6 @@
           <t>/Users/sebastianpasha/Developer/Environment_UNDP/PV2/Files/llm/brazil/brazil_budget_2024.xlsx</t>
         </is>
       </c>
-      <c r="K170" t="inlineStr">
-        <is>
-          <t>Comunicações</t>
-        </is>
-      </c>
     </row>
     <row r="171">
       <c r="A171" t="inlineStr">
@@ -9972,10 +10757,15 @@
       </c>
       <c r="K171" t="inlineStr">
         <is>
-          <t>Comunicações</t>
+          <t>standing_function</t>
         </is>
       </c>
       <c r="L171" t="inlineStr">
+        <is>
+          <t>model</t>
+        </is>
+      </c>
+      <c r="N171" t="inlineStr">
         <is>
           <t>PROGRAMA DE GESTAO E MANUTENCAO DO PODER EXECUTIVO</t>
         </is>
@@ -10032,10 +10822,15 @@
       </c>
       <c r="K172" t="inlineStr">
         <is>
-          <t>Comunicações</t>
+          <t>development</t>
         </is>
       </c>
       <c r="L172" t="inlineStr">
+        <is>
+          <t>model</t>
+        </is>
+      </c>
+      <c r="N172" t="inlineStr">
         <is>
           <t>COMUNICACOES PARA INCLUSAO E TRANSFORMACAO</t>
         </is>
@@ -10130,7 +10925,17 @@
           <t>/Users/sebastianpasha/Developer/Environment_UNDP/PV2/Files/llm/brazil/brazil_budget_2024.xlsx</t>
         </is>
       </c>
+      <c r="K174" t="inlineStr">
+        <is>
+          <t>standing_function</t>
+        </is>
+      </c>
       <c r="L174" t="inlineStr">
+        <is>
+          <t>model</t>
+        </is>
+      </c>
+      <c r="N174" t="inlineStr">
         <is>
           <t>PROGRAMA DE GESTAO E MANUTENCAO DO PODER EXECUTIVO</t>
         </is>
@@ -10185,6 +10990,16 @@
           <t>/Users/sebastianpasha/Developer/Environment_UNDP/PV2/Files/llm/brazil/brazil_budget_2024.xlsx</t>
         </is>
       </c>
+      <c r="K175" t="inlineStr">
+        <is>
+          <t>overhead</t>
+        </is>
+      </c>
+      <c r="L175" t="inlineStr">
+        <is>
+          <t>model</t>
+        </is>
+      </c>
     </row>
     <row r="176">
       <c r="A176" t="inlineStr">
@@ -10235,6 +11050,16 @@
           <t>/Users/sebastianpasha/Developer/Environment_UNDP/PV2/Files/llm/brazil/brazil_budget_2024.xlsx</t>
         </is>
       </c>
+      <c r="K176" t="inlineStr">
+        <is>
+          <t>development</t>
+        </is>
+      </c>
+      <c r="L176" t="inlineStr">
+        <is>
+          <t>model</t>
+        </is>
+      </c>
     </row>
     <row r="177">
       <c r="A177" t="inlineStr">
@@ -10285,6 +11110,16 @@
           <t>/Users/sebastianpasha/Developer/Environment_UNDP/PV2/Files/llm/brazil/brazil_budget_2024.xlsx</t>
         </is>
       </c>
+      <c r="K177" t="inlineStr">
+        <is>
+          <t>development</t>
+        </is>
+      </c>
+      <c r="L177" t="inlineStr">
+        <is>
+          <t>model</t>
+        </is>
+      </c>
     </row>
     <row r="178">
       <c r="A178" t="inlineStr">
@@ -10335,6 +11170,16 @@
           <t>/Users/sebastianpasha/Developer/Environment_UNDP/PV2/Files/llm/brazil/brazil_budget_2024.xlsx</t>
         </is>
       </c>
+      <c r="K178" t="inlineStr">
+        <is>
+          <t>development</t>
+        </is>
+      </c>
+      <c r="L178" t="inlineStr">
+        <is>
+          <t>model</t>
+        </is>
+      </c>
     </row>
     <row r="179">
       <c r="A179" t="inlineStr">
@@ -10425,7 +11270,17 @@
           <t>/Users/sebastianpasha/Developer/Environment_UNDP/PV2/Files/llm/brazil/brazil_budget_2024.xlsx</t>
         </is>
       </c>
+      <c r="K180" t="inlineStr">
+        <is>
+          <t>standing_function</t>
+        </is>
+      </c>
       <c r="L180" t="inlineStr">
+        <is>
+          <t>model</t>
+        </is>
+      </c>
+      <c r="N180" t="inlineStr">
         <is>
           <t>PROGRAMA DE GESTAO E MANUTENCAO DO PODER EXECUTIVO</t>
         </is>
@@ -10480,6 +11335,16 @@
           <t>/Users/sebastianpasha/Developer/Environment_UNDP/PV2/Files/llm/brazil/brazil_budget_2024.xlsx</t>
         </is>
       </c>
+      <c r="K181" t="inlineStr">
+        <is>
+          <t>overhead</t>
+        </is>
+      </c>
+      <c r="L181" t="inlineStr">
+        <is>
+          <t>model</t>
+        </is>
+      </c>
     </row>
     <row r="182">
       <c r="A182" t="inlineStr">
@@ -10530,7 +11395,17 @@
           <t>/Users/sebastianpasha/Developer/Environment_UNDP/PV2/Files/llm/brazil/brazil_budget_2024.xlsx</t>
         </is>
       </c>
+      <c r="K182" t="inlineStr">
+        <is>
+          <t>overhead</t>
+        </is>
+      </c>
       <c r="L182" t="inlineStr">
+        <is>
+          <t>model</t>
+        </is>
+      </c>
+      <c r="N182" t="inlineStr">
         <is>
           <t>OPERACOES ESPECIAIS: GESTAO DA PARTICIPACAO EM ORGANISMOS E</t>
         </is>
@@ -10585,6 +11460,16 @@
           <t>/Users/sebastianpasha/Developer/Environment_UNDP/PV2/Files/llm/brazil/brazil_budget_2024.xlsx</t>
         </is>
       </c>
+      <c r="K183" t="inlineStr">
+        <is>
+          <t>development</t>
+        </is>
+      </c>
+      <c r="L183" t="inlineStr">
+        <is>
+          <t>model</t>
+        </is>
+      </c>
     </row>
     <row r="184">
       <c r="A184" t="inlineStr">
@@ -10635,6 +11520,16 @@
           <t>/Users/sebastianpasha/Developer/Environment_UNDP/PV2/Files/llm/brazil/brazil_budget_2024.xlsx</t>
         </is>
       </c>
+      <c r="K184" t="inlineStr">
+        <is>
+          <t>development</t>
+        </is>
+      </c>
+      <c r="L184" t="inlineStr">
+        <is>
+          <t>model</t>
+        </is>
+      </c>
     </row>
     <row r="185">
       <c r="A185" t="inlineStr">
@@ -10685,6 +11580,16 @@
           <t>/Users/sebastianpasha/Developer/Environment_UNDP/PV2/Files/llm/brazil/brazil_budget_2024.xlsx</t>
         </is>
       </c>
+      <c r="K185" t="inlineStr">
+        <is>
+          <t>development</t>
+        </is>
+      </c>
+      <c r="L185" t="inlineStr">
+        <is>
+          <t>model</t>
+        </is>
+      </c>
     </row>
     <row r="186">
       <c r="A186" t="inlineStr">
@@ -10735,6 +11640,16 @@
           <t>/Users/sebastianpasha/Developer/Environment_UNDP/PV2/Files/llm/brazil/brazil_budget_2024.xlsx</t>
         </is>
       </c>
+      <c r="K186" t="inlineStr">
+        <is>
+          <t>development</t>
+        </is>
+      </c>
+      <c r="L186" t="inlineStr">
+        <is>
+          <t>model</t>
+        </is>
+      </c>
     </row>
     <row r="187">
       <c r="A187" t="inlineStr">
@@ -10785,6 +11700,16 @@
           <t>/Users/sebastianpasha/Developer/Environment_UNDP/PV2/Files/llm/brazil/brazil_budget_2024.xlsx</t>
         </is>
       </c>
+      <c r="K187" t="inlineStr">
+        <is>
+          <t>development</t>
+        </is>
+      </c>
+      <c r="L187" t="inlineStr">
+        <is>
+          <t>model</t>
+        </is>
+      </c>
     </row>
     <row r="188">
       <c r="A188" t="inlineStr">
@@ -10875,7 +11800,17 @@
           <t>/Users/sebastianpasha/Developer/Environment_UNDP/PV2/Files/llm/brazil/brazil_budget_2024.xlsx</t>
         </is>
       </c>
+      <c r="K189" t="inlineStr">
+        <is>
+          <t>standing_function</t>
+        </is>
+      </c>
       <c r="L189" t="inlineStr">
+        <is>
+          <t>model</t>
+        </is>
+      </c>
+      <c r="N189" t="inlineStr">
         <is>
           <t>PROGRAMA DE GESTAO E MANUTENCAO DO PODER EXECUTIVO</t>
         </is>
@@ -10930,7 +11865,17 @@
           <t>/Users/sebastianpasha/Developer/Environment_UNDP/PV2/Files/llm/brazil/brazil_budget_2024.xlsx</t>
         </is>
       </c>
+      <c r="K190" t="inlineStr">
+        <is>
+          <t>development</t>
+        </is>
+      </c>
       <c r="L190" t="inlineStr">
+        <is>
+          <t>model</t>
+        </is>
+      </c>
+      <c r="N190" t="inlineStr">
         <is>
           <t>ESPORTE PARA A VIDA</t>
         </is>
@@ -11025,7 +11970,17 @@
           <t>/Users/sebastianpasha/Developer/Environment_UNDP/PV2/Files/llm/brazil/brazil_budget_2024.xlsx</t>
         </is>
       </c>
+      <c r="K192" t="inlineStr">
+        <is>
+          <t>standing_function</t>
+        </is>
+      </c>
       <c r="L192" t="inlineStr">
+        <is>
+          <t>model</t>
+        </is>
+      </c>
+      <c r="N192" t="inlineStr">
         <is>
           <t>PROGRAMA DE GESTAO E MANUTENCAO DO PODER EXECUTIVO</t>
         </is>
@@ -11080,7 +12035,17 @@
           <t>/Users/sebastianpasha/Developer/Environment_UNDP/PV2/Files/llm/brazil/brazil_budget_2024.xlsx</t>
         </is>
       </c>
+      <c r="K193" t="inlineStr">
+        <is>
+          <t>overhead</t>
+        </is>
+      </c>
       <c r="L193" t="inlineStr">
+        <is>
+          <t>model</t>
+        </is>
+      </c>
+      <c r="N193" t="inlineStr">
         <is>
           <t>OPERACOES ESPECIAIS: CUMPRIMENTO DE SENTENCAS JUDICIAIS</t>
         </is>
@@ -11135,7 +12100,17 @@
           <t>/Users/sebastianpasha/Developer/Environment_UNDP/PV2/Files/llm/brazil/brazil_budget_2024.xlsx</t>
         </is>
       </c>
+      <c r="K194" t="inlineStr">
+        <is>
+          <t>overhead</t>
+        </is>
+      </c>
       <c r="L194" t="inlineStr">
+        <is>
+          <t>model</t>
+        </is>
+      </c>
+      <c r="N194" t="inlineStr">
         <is>
           <t>OPERACOES ESPECIAIS: FINANCIAMENTOS COM RETORNO</t>
         </is>
@@ -11190,6 +12165,16 @@
           <t>/Users/sebastianpasha/Developer/Environment_UNDP/PV2/Files/llm/brazil/brazil_budget_2024.xlsx</t>
         </is>
       </c>
+      <c r="K195" t="inlineStr">
+        <is>
+          <t>overhead</t>
+        </is>
+      </c>
+      <c r="L195" t="inlineStr">
+        <is>
+          <t>model</t>
+        </is>
+      </c>
     </row>
     <row r="196">
       <c r="A196" t="inlineStr">
@@ -11240,7 +12225,17 @@
           <t>/Users/sebastianpasha/Developer/Environment_UNDP/PV2/Files/llm/brazil/brazil_budget_2024.xlsx</t>
         </is>
       </c>
+      <c r="K196" t="inlineStr">
+        <is>
+          <t>overhead</t>
+        </is>
+      </c>
       <c r="L196" t="inlineStr">
+        <is>
+          <t>model</t>
+        </is>
+      </c>
+      <c r="N196" t="inlineStr">
         <is>
           <t>OPERACOES ESPECIAIS: SERVICO DA DIVIDA INTERNA (JUROS EAMORT</t>
         </is>
@@ -11295,7 +12290,17 @@
           <t>/Users/sebastianpasha/Developer/Environment_UNDP/PV2/Files/llm/brazil/brazil_budget_2024.xlsx</t>
         </is>
       </c>
+      <c r="K197" t="inlineStr">
+        <is>
+          <t>overhead</t>
+        </is>
+      </c>
       <c r="L197" t="inlineStr">
+        <is>
+          <t>model</t>
+        </is>
+      </c>
+      <c r="N197" t="inlineStr">
         <is>
           <t>OPERACOES ESPECIAIS: SERVICO DA DIVIDA EXTERNA (JUROS EAMORT</t>
         </is>
@@ -11350,7 +12355,17 @@
           <t>/Users/sebastianpasha/Developer/Environment_UNDP/PV2/Files/llm/brazil/brazil_budget_2024.xlsx</t>
         </is>
       </c>
+      <c r="K198" t="inlineStr">
+        <is>
+          <t>overhead</t>
+        </is>
+      </c>
       <c r="L198" t="inlineStr">
+        <is>
+          <t>model</t>
+        </is>
+      </c>
+      <c r="N198" t="inlineStr">
         <is>
           <t>OPERACOES ESPECIAIS: REFINANCIAMENTO DA DIVIDA INTERNA</t>
         </is>
@@ -11405,7 +12420,17 @@
           <t>/Users/sebastianpasha/Developer/Environment_UNDP/PV2/Files/llm/brazil/brazil_budget_2024.xlsx</t>
         </is>
       </c>
+      <c r="K199" t="inlineStr">
+        <is>
+          <t>overhead</t>
+        </is>
+      </c>
       <c r="L199" t="inlineStr">
+        <is>
+          <t>model</t>
+        </is>
+      </c>
+      <c r="N199" t="inlineStr">
         <is>
           <t>OPERACOES ESPECIAIS: REFINANCIAMENTO DA DIVIDA EXTERNA</t>
         </is>
@@ -11460,6 +12485,16 @@
           <t>/Users/sebastianpasha/Developer/Environment_UNDP/PV2/Files/llm/brazil/brazil_budget_2024.xlsx</t>
         </is>
       </c>
+      <c r="K200" t="inlineStr">
+        <is>
+          <t>overhead</t>
+        </is>
+      </c>
+      <c r="L200" t="inlineStr">
+        <is>
+          <t>model</t>
+        </is>
+      </c>
     </row>
     <row r="201">
       <c r="A201" t="inlineStr">
@@ -11510,7 +12545,17 @@
           <t>/Users/sebastianpasha/Developer/Environment_UNDP/PV2/Files/llm/brazil/brazil_budget_2024.xlsx</t>
         </is>
       </c>
+      <c r="K201" t="inlineStr">
+        <is>
+          <t>overhead</t>
+        </is>
+      </c>
       <c r="L201" t="inlineStr">
+        <is>
+          <t>model</t>
+        </is>
+      </c>
+      <c r="N201" t="inlineStr">
         <is>
           <t>OPERACOES ESPECIAIS: GESTAO DA PARTICIPACAO EM ORGANISMOS E</t>
         </is>
@@ -11565,7 +12610,17 @@
           <t>/Users/sebastianpasha/Developer/Environment_UNDP/PV2/Files/llm/brazil/brazil_budget_2024.xlsx</t>
         </is>
       </c>
+      <c r="K202" t="inlineStr">
+        <is>
+          <t>overhead</t>
+        </is>
+      </c>
       <c r="L202" t="inlineStr">
+        <is>
+          <t>model</t>
+        </is>
+      </c>
+      <c r="N202" t="inlineStr">
         <is>
           <t>OPERACOES ESPECIAIS - REMUNERACAO DE AGENTES FINANCEIROS</t>
         </is>
@@ -11620,7 +12675,17 @@
           <t>/Users/sebastianpasha/Developer/Environment_UNDP/PV2/Files/llm/brazil/brazil_budget_2024.xlsx</t>
         </is>
       </c>
+      <c r="K203" t="inlineStr">
+        <is>
+          <t>overhead</t>
+        </is>
+      </c>
       <c r="L203" t="inlineStr">
+        <is>
+          <t>model</t>
+        </is>
+      </c>
+      <c r="N203" t="inlineStr">
         <is>
           <t>OPERACOES ESPECIAIS - INTEGRALIZACAO DE COTAS EM BANCOSINTER</t>
         </is>
@@ -11675,6 +12740,16 @@
           <t>/Users/sebastianpasha/Developer/Environment_UNDP/PV2/Files/llm/brazil/brazil_budget_2024.xlsx</t>
         </is>
       </c>
+      <c r="K204" t="inlineStr">
+        <is>
+          <t>development</t>
+        </is>
+      </c>
+      <c r="L204" t="inlineStr">
+        <is>
+          <t>model</t>
+        </is>
+      </c>
     </row>
     <row r="205">
       <c r="A205" t="inlineStr">
@@ -11725,7 +12800,17 @@
           <t>/Users/sebastianpasha/Developer/Environment_UNDP/PV2/Files/llm/brazil/brazil_budget_2024.xlsx</t>
         </is>
       </c>
+      <c r="K205" t="inlineStr">
+        <is>
+          <t>development</t>
+        </is>
+      </c>
       <c r="L205" t="inlineStr">
+        <is>
+          <t>model</t>
+        </is>
+      </c>
+      <c r="N205" t="inlineStr">
         <is>
           <t>DESENVOLVIMENTO REGIONAL E ORDENAMENTO TERRITORIAL</t>
         </is>
@@ -11780,7 +12865,17 @@
           <t>/Users/sebastianpasha/Developer/Environment_UNDP/PV2/Files/llm/brazil/brazil_budget_2024.xlsx</t>
         </is>
       </c>
+      <c r="K206" t="inlineStr">
+        <is>
+          <t>development</t>
+        </is>
+      </c>
       <c r="L206" t="inlineStr">
+        <is>
+          <t>model</t>
+        </is>
+      </c>
+      <c r="N206" t="inlineStr">
         <is>
           <t>GESTAO DE RISCOS E DE DESASTRES</t>
         </is>
@@ -11835,6 +12930,16 @@
           <t>/Users/sebastianpasha/Developer/Environment_UNDP/PV2/Files/llm/brazil/brazil_budget_2024.xlsx</t>
         </is>
       </c>
+      <c r="K207" t="inlineStr">
+        <is>
+          <t>development</t>
+        </is>
+      </c>
+      <c r="L207" t="inlineStr">
+        <is>
+          <t>model</t>
+        </is>
+      </c>
     </row>
     <row r="208">
       <c r="A208" t="inlineStr">
@@ -11885,7 +12990,17 @@
           <t>/Users/sebastianpasha/Developer/Environment_UNDP/PV2/Files/llm/brazil/brazil_budget_2024.xlsx</t>
         </is>
       </c>
+      <c r="K208" t="inlineStr">
+        <is>
+          <t>development</t>
+        </is>
+      </c>
       <c r="L208" t="inlineStr">
+        <is>
+          <t>model</t>
+        </is>
+      </c>
+      <c r="N208" t="inlineStr">
         <is>
           <t>PROMOCAO DA CIDADANIA, DEFESA DE DIREITOS HUMANOS E REPARACA</t>
         </is>
@@ -11930,11 +13045,6 @@
           <t>/Users/sebastianpasha/Developer/Environment_UNDP/PV2/Files/llm/brazil/brazil_budget_2024.xlsx</t>
         </is>
       </c>
-      <c r="K209" t="inlineStr">
-        <is>
-          <t>Reserva de contingência</t>
-        </is>
-      </c>
     </row>
     <row r="210">
       <c r="A210" t="inlineStr">
@@ -11987,10 +13097,15 @@
       </c>
       <c r="K210" t="inlineStr">
         <is>
-          <t>Reserva de contingência</t>
+          <t>overhead</t>
         </is>
       </c>
       <c r="L210" t="inlineStr">
+        <is>
+          <t>model</t>
+        </is>
+      </c>
+      <c r="N210" t="inlineStr">
         <is>
           <t>OPERACOES ESPECIAIS: CUMPRIMENTO DE SENTENCAS JUDICIAIS</t>
         </is>
@@ -12047,10 +13162,15 @@
       </c>
       <c r="K211" t="inlineStr">
         <is>
-          <t>Reserva de contingência</t>
+          <t>overhead</t>
         </is>
       </c>
       <c r="L211" t="inlineStr">
+        <is>
+          <t>model</t>
+        </is>
+      </c>
+      <c r="N211" t="inlineStr">
         <is>
           <t>RESERVA DE CONTINGENCIA</t>
         </is>

--- a/brazil/budget_layer_all_years.xlsx
+++ b/brazil/budget_layer_all_years.xlsx
@@ -9,8 +9,9 @@
   <sheets>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="budget_all_years" sheetId="1" state="visible" r:id="rId1"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="programs_wide" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="reconciliation" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="data_quality" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="national_total" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="reconciliation" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="data_quality" sheetId="5" state="visible" r:id="rId5"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -17513,7 +17514,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F29"/>
+  <dimension ref="A1:G2"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -17524,27 +17525,32 @@
       </c>
       <c r="B1" t="inlineStr">
         <is>
-          <t>strategy_code</t>
+          <t>head_total</t>
         </is>
       </c>
       <c r="C1" t="inlineStr">
         <is>
-          <t>strategy_total</t>
+          <t>programme_total</t>
         </is>
       </c>
       <c r="D1" t="inlineStr">
         <is>
-          <t>program_sum</t>
+          <t>gap_pct</t>
         </is>
       </c>
       <c r="E1" t="inlineStr">
         <is>
-          <t>diff</t>
+          <t>basis</t>
         </is>
       </c>
       <c r="F1" t="inlineStr">
         <is>
-          <t>status</t>
+          <t>nested_heads</t>
+        </is>
+      </c>
+      <c r="G1" t="inlineStr">
+        <is>
+          <t>national</t>
         </is>
       </c>
     </row>
@@ -17554,726 +17560,25 @@
           <t>2024</t>
         </is>
       </c>
-      <c r="B2" t="inlineStr">
-        <is>
-          <t>02</t>
-        </is>
+      <c r="B2" t="n">
+        <v>5323812.22</v>
       </c>
       <c r="C2" t="n">
-        <v>0</v>
+        <v>5323334.271</v>
       </c>
       <c r="D2" t="n">
-        <v>0</v>
-      </c>
-      <c r="E2" t="n">
-        <v>0</v>
-      </c>
-      <c r="F2" t="inlineStr">
-        <is>
-          <t>OK</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>2024</t>
-        </is>
-      </c>
-      <c r="B3" t="inlineStr">
-        <is>
-          <t>03</t>
-        </is>
-      </c>
-      <c r="C3" t="n">
-        <v>947.481</v>
-      </c>
-      <c r="D3" t="n">
-        <v>947.481</v>
-      </c>
-      <c r="E3" t="n">
-        <v>0</v>
-      </c>
-      <c r="F3" t="inlineStr">
-        <is>
-          <t>OK</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>2024</t>
-        </is>
-      </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>04</t>
-        </is>
-      </c>
-      <c r="C4" t="n">
-        <v>32101.792</v>
-      </c>
-      <c r="D4" t="n">
-        <v>32101.79099999999</v>
-      </c>
-      <c r="E4" t="n">
-        <v>0.001000000011117663</v>
-      </c>
-      <c r="F4" t="inlineStr">
-        <is>
-          <t>OK</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>2024</t>
-        </is>
-      </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>05</t>
-        </is>
-      </c>
-      <c r="C5" t="n">
-        <v>92730.663</v>
-      </c>
-      <c r="D5" t="n">
-        <v>92730.66299999999</v>
-      </c>
-      <c r="E5" t="n">
-        <v>1.455191522836685e-11</v>
-      </c>
-      <c r="F5" t="inlineStr">
-        <is>
-          <t>OK</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>2024</t>
-        </is>
-      </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>06</t>
-        </is>
-      </c>
-      <c r="C6" t="n">
-        <v>16664.296</v>
-      </c>
-      <c r="D6" t="n">
-        <v>16664.296</v>
-      </c>
-      <c r="E6" t="n">
-        <v>-3.637978807091713e-12</v>
-      </c>
-      <c r="F6" t="inlineStr">
-        <is>
-          <t>OK</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>2024</t>
-        </is>
-      </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>07</t>
-        </is>
-      </c>
-      <c r="C7" t="n">
-        <v>4135.507</v>
-      </c>
-      <c r="D7" t="n">
-        <v>4135.507</v>
-      </c>
-      <c r="E7" t="n">
-        <v>0</v>
-      </c>
-      <c r="F7" t="inlineStr">
-        <is>
-          <t>OK</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t>2024</t>
-        </is>
-      </c>
-      <c r="B8" t="inlineStr">
-        <is>
-          <t>08</t>
-        </is>
-      </c>
-      <c r="C8" t="n">
-        <v>278581.467</v>
-      </c>
-      <c r="D8" t="n">
-        <v>278581.4670000001</v>
-      </c>
-      <c r="E8" t="n">
-        <v>-5.820766091346741e-11</v>
-      </c>
-      <c r="F8" t="inlineStr">
-        <is>
-          <t>OK</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="inlineStr">
-        <is>
-          <t>2024</t>
-        </is>
-      </c>
-      <c r="B9" t="inlineStr">
-        <is>
-          <t>09</t>
-        </is>
-      </c>
-      <c r="C9" t="n">
-        <v>1002681.586</v>
-      </c>
-      <c r="D9" t="n">
-        <v>1002681.587</v>
-      </c>
-      <c r="E9" t="n">
-        <v>-0.001000000047497451</v>
-      </c>
-      <c r="F9" t="inlineStr">
-        <is>
-          <t>OK</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t>2024</t>
-        </is>
-      </c>
-      <c r="B10" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="C10" t="n">
-        <v>219826.755</v>
-      </c>
-      <c r="D10" t="n">
-        <v>219826.754</v>
-      </c>
-      <c r="E10" t="n">
-        <v>0.0009999999601859599</v>
-      </c>
-      <c r="F10" t="inlineStr">
-        <is>
-          <t>OK</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="inlineStr">
-        <is>
-          <t>2024</t>
-        </is>
-      </c>
-      <c r="B11" t="inlineStr">
-        <is>
-          <t>11</t>
-        </is>
-      </c>
-      <c r="C11" t="n">
-        <v>107634.125</v>
-      </c>
-      <c r="D11" t="n">
-        <v>107634.125</v>
-      </c>
-      <c r="E11" t="n">
-        <v>0</v>
-      </c>
-      <c r="F11" t="inlineStr">
-        <is>
-          <t>OK</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="inlineStr">
-        <is>
-          <t>2024</t>
-        </is>
-      </c>
-      <c r="B12" t="inlineStr">
-        <is>
-          <t>12</t>
-        </is>
-      </c>
-      <c r="C12" t="n">
-        <v>162614.024</v>
-      </c>
-      <c r="D12" t="n">
-        <v>162614.025</v>
-      </c>
-      <c r="E12" t="n">
-        <v>-0.001000000018393621</v>
-      </c>
-      <c r="F12" t="inlineStr">
-        <is>
-          <t>OK</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" t="inlineStr">
-        <is>
-          <t>2024</t>
-        </is>
-      </c>
-      <c r="B13" t="inlineStr">
-        <is>
-          <t>13</t>
-        </is>
-      </c>
-      <c r="C13" t="n">
-        <v>2877.345</v>
-      </c>
-      <c r="D13" t="n">
-        <v>2877.345</v>
-      </c>
-      <c r="E13" t="n">
-        <v>0</v>
-      </c>
-      <c r="F13" t="inlineStr">
-        <is>
-          <t>OK</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="inlineStr">
-        <is>
-          <t>2024</t>
-        </is>
-      </c>
-      <c r="B14" t="inlineStr">
-        <is>
-          <t>14</t>
-        </is>
-      </c>
-      <c r="C14" t="n">
-        <v>2170.599</v>
-      </c>
-      <c r="D14" t="n">
-        <v>2170.599</v>
-      </c>
-      <c r="E14" t="n">
-        <v>0</v>
-      </c>
-      <c r="F14" t="inlineStr">
-        <is>
-          <t>OK</t>
-        </is>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" t="inlineStr">
-        <is>
-          <t>2024</t>
-        </is>
-      </c>
-      <c r="B15" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
-      </c>
-      <c r="C15" t="n">
-        <v>10239.386</v>
-      </c>
-      <c r="D15" t="n">
-        <v>10239.387</v>
-      </c>
-      <c r="E15" t="n">
-        <v>-0.0009999999983847374</v>
-      </c>
-      <c r="F15" t="inlineStr">
-        <is>
-          <t>OK</t>
-        </is>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" t="inlineStr">
-        <is>
-          <t>2024</t>
-        </is>
-      </c>
-      <c r="B16" t="inlineStr">
-        <is>
-          <t>16</t>
-        </is>
-      </c>
-      <c r="C16" t="n">
-        <v>682.617</v>
-      </c>
-      <c r="D16" t="n">
-        <v>682.617</v>
-      </c>
-      <c r="E16" t="n">
-        <v>0</v>
-      </c>
-      <c r="F16" t="inlineStr">
-        <is>
-          <t>OK</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" t="inlineStr">
-        <is>
-          <t>2024</t>
-        </is>
-      </c>
-      <c r="B17" t="inlineStr">
-        <is>
-          <t>17</t>
-        </is>
-      </c>
-      <c r="C17" t="n">
-        <v>2937.235</v>
-      </c>
-      <c r="D17" t="n">
-        <v>2937.234</v>
-      </c>
-      <c r="E17" t="n">
-        <v>0.001000000000203727</v>
-      </c>
-      <c r="F17" t="inlineStr">
-        <is>
-          <t>OK</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" t="inlineStr">
-        <is>
-          <t>2024</t>
-        </is>
-      </c>
-      <c r="B18" t="inlineStr">
-        <is>
-          <t>18</t>
-        </is>
-      </c>
-      <c r="C18" t="n">
-        <v>15386.176</v>
-      </c>
-      <c r="D18" t="n">
-        <v>15386.177</v>
-      </c>
-      <c r="E18" t="n">
-        <v>-0.0009999999983847374</v>
-      </c>
-      <c r="F18" t="inlineStr">
-        <is>
-          <t>OK</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" t="inlineStr">
-        <is>
-          <t>2024</t>
-        </is>
-      </c>
-      <c r="B19" t="inlineStr">
-        <is>
-          <t>19</t>
-        </is>
-      </c>
-      <c r="C19" t="n">
-        <v>17427.157</v>
-      </c>
-      <c r="D19" t="n">
-        <v>17427.157</v>
-      </c>
-      <c r="E19" t="n">
-        <v>0</v>
-      </c>
-      <c r="F19" t="inlineStr">
-        <is>
-          <t>OK</t>
-        </is>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" t="inlineStr">
-        <is>
-          <t>2024</t>
-        </is>
-      </c>
-      <c r="B20" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
-      <c r="C20" t="n">
-        <v>29160.377</v>
-      </c>
-      <c r="D20" t="n">
-        <v>29160.377</v>
-      </c>
-      <c r="E20" t="n">
-        <v>0</v>
-      </c>
-      <c r="F20" t="inlineStr">
-        <is>
-          <t>OK</t>
-        </is>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" t="inlineStr">
-        <is>
-          <t>2024</t>
-        </is>
-      </c>
-      <c r="B21" t="inlineStr">
-        <is>
-          <t>21</t>
-        </is>
-      </c>
-      <c r="C21" t="n">
-        <v>3304.874</v>
-      </c>
-      <c r="D21" t="n">
-        <v>3304.874</v>
-      </c>
-      <c r="E21" t="n">
-        <v>0</v>
-      </c>
-      <c r="F21" t="inlineStr">
-        <is>
-          <t>OK</t>
-        </is>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" t="inlineStr">
-        <is>
-          <t>2024</t>
-        </is>
-      </c>
-      <c r="B22" t="inlineStr">
-        <is>
-          <t>22</t>
-        </is>
-      </c>
-      <c r="C22" t="n">
-        <v>2255.568</v>
-      </c>
-      <c r="D22" t="n">
-        <v>2255.568</v>
-      </c>
-      <c r="E22" t="n">
-        <v>4.547473508864641e-13</v>
-      </c>
-      <c r="F22" t="inlineStr">
-        <is>
-          <t>OK</t>
-        </is>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" t="inlineStr">
-        <is>
-          <t>2024</t>
-        </is>
-      </c>
-      <c r="B23" t="inlineStr">
-        <is>
-          <t>23</t>
-        </is>
-      </c>
-      <c r="C23" t="n">
-        <v>6197.025</v>
-      </c>
-      <c r="D23" t="n">
-        <v>6197.023999999999</v>
-      </c>
-      <c r="E23" t="n">
-        <v>0.001000000000203727</v>
-      </c>
-      <c r="F23" t="inlineStr">
-        <is>
-          <t>OK</t>
-        </is>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" t="inlineStr">
-        <is>
-          <t>2024</t>
-        </is>
-      </c>
-      <c r="B24" t="inlineStr">
-        <is>
-          <t>24</t>
-        </is>
-      </c>
-      <c r="C24" t="n">
-        <v>3006.756</v>
-      </c>
-      <c r="D24" t="n">
-        <v>3006.756</v>
-      </c>
-      <c r="E24" t="n">
-        <v>-4.547473508864641e-13</v>
-      </c>
-      <c r="F24" t="inlineStr">
-        <is>
-          <t>OK</t>
-        </is>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" t="inlineStr">
-        <is>
-          <t>2024</t>
-        </is>
-      </c>
-      <c r="B25" t="inlineStr">
-        <is>
-          <t>25</t>
-        </is>
-      </c>
-      <c r="C25" t="n">
-        <v>1289.543</v>
-      </c>
-      <c r="D25" t="n">
-        <v>1289.544</v>
-      </c>
-      <c r="E25" t="n">
-        <v>-0.0009999999999763531</v>
-      </c>
-      <c r="F25" t="inlineStr">
-        <is>
-          <t>OK</t>
-        </is>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" t="inlineStr">
-        <is>
-          <t>2024</t>
-        </is>
-      </c>
-      <c r="B26" t="inlineStr">
-        <is>
-          <t>26</t>
-        </is>
-      </c>
-      <c r="C26" t="n">
-        <v>27266.495</v>
-      </c>
-      <c r="D26" t="n">
-        <v>27266.494</v>
-      </c>
-      <c r="E26" t="n">
-        <v>0.001000000000203727</v>
-      </c>
-      <c r="F26" t="inlineStr">
-        <is>
-          <t>OK</t>
-        </is>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" t="inlineStr">
-        <is>
-          <t>2024</t>
-        </is>
-      </c>
-      <c r="B27" t="inlineStr">
-        <is>
-          <t>27</t>
-        </is>
-      </c>
-      <c r="C27" t="n">
-        <v>2077.96</v>
-      </c>
-      <c r="D27" t="n">
-        <v>2077.961</v>
-      </c>
-      <c r="E27" t="n">
-        <v>-0.0009999999997489795</v>
-      </c>
-      <c r="F27" t="inlineStr">
-        <is>
-          <t>OK</t>
-        </is>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" t="inlineStr">
-        <is>
-          <t>2024</t>
-        </is>
-      </c>
-      <c r="B28" t="inlineStr">
-        <is>
-          <t>28</t>
-        </is>
-      </c>
-      <c r="C28" t="n">
-        <v>3188051.922</v>
-      </c>
-      <c r="D28" t="n">
-        <v>3188051.922999999</v>
-      </c>
-      <c r="E28" t="n">
-        <v>-0.0009999996982514858</v>
-      </c>
-      <c r="F28" t="inlineStr">
-        <is>
-          <t>OK</t>
-        </is>
-      </c>
-    </row>
-    <row r="29">
-      <c r="A29" t="inlineStr">
-        <is>
-          <t>2024</t>
-        </is>
-      </c>
-      <c r="B29" t="inlineStr">
-        <is>
-          <t>99</t>
-        </is>
-      </c>
-      <c r="C29" t="n">
-        <v>91563.489</v>
-      </c>
-      <c r="D29" t="n">
-        <v>91563.48899999999</v>
-      </c>
-      <c r="E29" t="n">
-        <v>1.455191522836685e-11</v>
-      </c>
-      <c r="F29" t="inlineStr">
-        <is>
-          <t>OK</t>
-        </is>
+        <v>0.01</v>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>heads</t>
+        </is>
+      </c>
+      <c r="F2" t="n">
+        <v>1</v>
+      </c>
+      <c r="G2" t="n">
+        <v>5323812.22</v>
       </c>
     </row>
   </sheetData>
@@ -18287,58 +17592,960 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F2"/>
+  <dimension ref="A1:F29"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
-          <t>severity</t>
+          <t>fiscal_year</t>
         </is>
       </c>
       <c r="B1" t="inlineStr">
         <is>
-          <t>type</t>
+          <t>strategy_code</t>
         </is>
       </c>
       <c r="C1" t="inlineStr">
         <is>
-          <t>fiscal_year</t>
+          <t>strategy_total</t>
         </is>
       </c>
       <c r="D1" t="inlineStr">
         <is>
-          <t>strategy_code</t>
+          <t>program_sum</t>
         </is>
       </c>
       <c r="E1" t="inlineStr">
         <is>
-          <t>program_code</t>
+          <t>diff</t>
         </is>
       </c>
       <c r="F1" t="inlineStr">
         <is>
-          <t>detail</t>
+          <t>status</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
+          <t>2024</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>02</t>
+        </is>
+      </c>
+      <c r="C2" t="n">
+        <v>0</v>
+      </c>
+      <c r="D2" t="n">
+        <v>0</v>
+      </c>
+      <c r="E2" t="n">
+        <v>0</v>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>2024</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>03</t>
+        </is>
+      </c>
+      <c r="C3" t="n">
+        <v>947.481</v>
+      </c>
+      <c r="D3" t="n">
+        <v>947.481</v>
+      </c>
+      <c r="E3" t="n">
+        <v>0</v>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>2024</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>04</t>
+        </is>
+      </c>
+      <c r="C4" t="n">
+        <v>32101.792</v>
+      </c>
+      <c r="D4" t="n">
+        <v>32101.79099999999</v>
+      </c>
+      <c r="E4" t="n">
+        <v>0.001000000011117663</v>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>2024</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>05</t>
+        </is>
+      </c>
+      <c r="C5" t="n">
+        <v>92730.663</v>
+      </c>
+      <c r="D5" t="n">
+        <v>92730.66299999999</v>
+      </c>
+      <c r="E5" t="n">
+        <v>1.455191522836685e-11</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>2024</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>06</t>
+        </is>
+      </c>
+      <c r="C6" t="n">
+        <v>16664.296</v>
+      </c>
+      <c r="D6" t="n">
+        <v>16664.296</v>
+      </c>
+      <c r="E6" t="n">
+        <v>-3.637978807091713e-12</v>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>2024</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>07</t>
+        </is>
+      </c>
+      <c r="C7" t="n">
+        <v>4135.507</v>
+      </c>
+      <c r="D7" t="n">
+        <v>4135.507</v>
+      </c>
+      <c r="E7" t="n">
+        <v>0</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>2024</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>08</t>
+        </is>
+      </c>
+      <c r="C8" t="n">
+        <v>278581.467</v>
+      </c>
+      <c r="D8" t="n">
+        <v>278581.4670000001</v>
+      </c>
+      <c r="E8" t="n">
+        <v>-5.820766091346741e-11</v>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>2024</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>09</t>
+        </is>
+      </c>
+      <c r="C9" t="n">
+        <v>1002681.586</v>
+      </c>
+      <c r="D9" t="n">
+        <v>1002681.587</v>
+      </c>
+      <c r="E9" t="n">
+        <v>-0.001000000047497451</v>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>2024</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="C10" t="n">
+        <v>219826.755</v>
+      </c>
+      <c r="D10" t="n">
+        <v>219826.754</v>
+      </c>
+      <c r="E10" t="n">
+        <v>0.0009999999601859599</v>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>2024</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="C11" t="n">
+        <v>107634.125</v>
+      </c>
+      <c r="D11" t="n">
+        <v>107634.125</v>
+      </c>
+      <c r="E11" t="n">
+        <v>0</v>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>2024</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="C12" t="n">
+        <v>162614.024</v>
+      </c>
+      <c r="D12" t="n">
+        <v>162614.025</v>
+      </c>
+      <c r="E12" t="n">
+        <v>-0.001000000018393621</v>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>2024</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="C13" t="n">
+        <v>2877.345</v>
+      </c>
+      <c r="D13" t="n">
+        <v>2877.345</v>
+      </c>
+      <c r="E13" t="n">
+        <v>0</v>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>2024</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="C14" t="n">
+        <v>2170.599</v>
+      </c>
+      <c r="D14" t="n">
+        <v>2170.599</v>
+      </c>
+      <c r="E14" t="n">
+        <v>0</v>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>2024</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="C15" t="n">
+        <v>10239.386</v>
+      </c>
+      <c r="D15" t="n">
+        <v>10239.387</v>
+      </c>
+      <c r="E15" t="n">
+        <v>-0.0009999999983847374</v>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>2024</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="C16" t="n">
+        <v>682.617</v>
+      </c>
+      <c r="D16" t="n">
+        <v>682.617</v>
+      </c>
+      <c r="E16" t="n">
+        <v>0</v>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>2024</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>17</t>
+        </is>
+      </c>
+      <c r="C17" t="n">
+        <v>2937.235</v>
+      </c>
+      <c r="D17" t="n">
+        <v>2937.234</v>
+      </c>
+      <c r="E17" t="n">
+        <v>0.001000000000203727</v>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>2024</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>18</t>
+        </is>
+      </c>
+      <c r="C18" t="n">
+        <v>15386.176</v>
+      </c>
+      <c r="D18" t="n">
+        <v>15386.177</v>
+      </c>
+      <c r="E18" t="n">
+        <v>-0.0009999999983847374</v>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>2024</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>19</t>
+        </is>
+      </c>
+      <c r="C19" t="n">
+        <v>17427.157</v>
+      </c>
+      <c r="D19" t="n">
+        <v>17427.157</v>
+      </c>
+      <c r="E19" t="n">
+        <v>0</v>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>2024</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="C20" t="n">
+        <v>29160.377</v>
+      </c>
+      <c r="D20" t="n">
+        <v>29160.377</v>
+      </c>
+      <c r="E20" t="n">
+        <v>0</v>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>2024</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>21</t>
+        </is>
+      </c>
+      <c r="C21" t="n">
+        <v>3304.874</v>
+      </c>
+      <c r="D21" t="n">
+        <v>3304.874</v>
+      </c>
+      <c r="E21" t="n">
+        <v>0</v>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>2024</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>22</t>
+        </is>
+      </c>
+      <c r="C22" t="n">
+        <v>2255.568</v>
+      </c>
+      <c r="D22" t="n">
+        <v>2255.568</v>
+      </c>
+      <c r="E22" t="n">
+        <v>4.547473508864641e-13</v>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>2024</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>23</t>
+        </is>
+      </c>
+      <c r="C23" t="n">
+        <v>6197.025</v>
+      </c>
+      <c r="D23" t="n">
+        <v>6197.023999999999</v>
+      </c>
+      <c r="E23" t="n">
+        <v>0.001000000000203727</v>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>2024</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>24</t>
+        </is>
+      </c>
+      <c r="C24" t="n">
+        <v>3006.756</v>
+      </c>
+      <c r="D24" t="n">
+        <v>3006.756</v>
+      </c>
+      <c r="E24" t="n">
+        <v>-4.547473508864641e-13</v>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>2024</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="C25" t="n">
+        <v>1289.543</v>
+      </c>
+      <c r="D25" t="n">
+        <v>1289.544</v>
+      </c>
+      <c r="E25" t="n">
+        <v>-0.0009999999999763531</v>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>2024</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>26</t>
+        </is>
+      </c>
+      <c r="C26" t="n">
+        <v>27266.495</v>
+      </c>
+      <c r="D26" t="n">
+        <v>27266.494</v>
+      </c>
+      <c r="E26" t="n">
+        <v>0.001000000000203727</v>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>2024</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>27</t>
+        </is>
+      </c>
+      <c r="C27" t="n">
+        <v>2077.96</v>
+      </c>
+      <c r="D27" t="n">
+        <v>2077.961</v>
+      </c>
+      <c r="E27" t="n">
+        <v>-0.0009999999997489795</v>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>2024</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>28</t>
+        </is>
+      </c>
+      <c r="C28" t="n">
+        <v>3188051.922</v>
+      </c>
+      <c r="D28" t="n">
+        <v>3188051.922999999</v>
+      </c>
+      <c r="E28" t="n">
+        <v>-0.0009999996982514858</v>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>2024</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>99</t>
+        </is>
+      </c>
+      <c r="C29" t="n">
+        <v>91563.489</v>
+      </c>
+      <c r="D29" t="n">
+        <v>91563.48899999999</v>
+      </c>
+      <c r="E29" t="n">
+        <v>1.455191522836685e-11</v>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:F6"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>severity</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>type</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>fiscal_year</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>strategy_code</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>program_code</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
+        <is>
+          <t>detail</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>MEDIUM</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>zero_amount_programme</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>2024</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>02</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>0033</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>programme carries no money; a strategy matched only to lines like this reads as funded while receiving nothing</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>MEDIUM</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>zero_amount_programme</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>2024</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>0151</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>programme carries no money; a strategy matched only to lines like this reads as funded while receiving nothing</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>MEDIUM</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>zero_amount_programme</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>2024</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>23</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>0909</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>programme carries no money; a strategy matched only to lines like this reads as funded while receiving nothing</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>MEDIUM</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>zero_amount_programme</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>2024</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>28</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>1144</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>programme carries no money; a strategy matched only to lines like this reads as funded while receiving nothing</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
           <t>INFO</t>
         </is>
       </c>
-      <c r="B2" t="inlineStr">
+      <c r="B6" t="inlineStr">
         <is>
           <t>national_total</t>
         </is>
       </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>2024</t>
-        </is>
-      </c>
-      <c r="F2" t="inlineStr">
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>2024</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
         <is>
           <t>national budget total = 5,323,812.2</t>
         </is>

--- a/brazil/budget_layer_all_years.xlsx
+++ b/brazil/budget_layer_all_years.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N211"/>
+  <dimension ref="A1:O211"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -488,6 +488,11 @@
       </c>
       <c r="N1" t="inlineStr">
         <is>
+          <t>countable</t>
+        </is>
+      </c>
+      <c r="O1" t="inlineStr">
+        <is>
           <t>program_name_source</t>
         </is>
       </c>
@@ -593,6 +598,11 @@
       </c>
       <c r="N3" t="inlineStr">
         <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="O3" t="inlineStr">
+        <is>
           <t>PROGRAMA DE GESTAO E MANUTENCAO DO PODER JUDICIARIO</t>
         </is>
       </c>
@@ -698,6 +708,11 @@
       </c>
       <c r="N5" t="inlineStr">
         <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="O5" t="inlineStr">
+        <is>
           <t>PROGRAMA DE GESTAO E MANUTENCAO DO PODER EXECUTIVO</t>
         </is>
       </c>
@@ -763,6 +778,11 @@
       </c>
       <c r="N6" t="inlineStr">
         <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="O6" t="inlineStr">
+        <is>
           <t>DEFESA DA DEMOCRACIA E SEGURANCA JURIDICA PARA INOVACAOEM PO</t>
         </is>
       </c>
@@ -868,6 +888,11 @@
       </c>
       <c r="N8" t="inlineStr">
         <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="O8" t="inlineStr">
+        <is>
           <t>PROGRAMA DE GESTAO E MANUTENCAO DO PODER EXECUTIVO</t>
         </is>
       </c>
@@ -931,6 +956,11 @@
           <t>model</t>
         </is>
       </c>
+      <c r="N9" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -993,6 +1023,11 @@
       </c>
       <c r="N10" t="inlineStr">
         <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="O10" t="inlineStr">
+        <is>
           <t>RECONSTRUCAO, AMPLIACAO E APROFUNDAMENTO DA PARTICIPACAO SOC</t>
         </is>
       </c>
@@ -1058,6 +1093,11 @@
       </c>
       <c r="N11" t="inlineStr">
         <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="O11" t="inlineStr">
+        <is>
           <t>PLANEJAMENTO E ORCAMENTO PARA O DESENVOLVIMENTO SUSTENTAVEL</t>
         </is>
       </c>
@@ -1123,6 +1163,11 @@
       </c>
       <c r="N12" t="inlineStr">
         <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="O12" t="inlineStr">
+        <is>
           <t>TRANSFORMACAO DO ESTADO PARA A CIDADANIA E O DESENVOLVIMENTO</t>
         </is>
       </c>
@@ -1188,6 +1233,11 @@
       </c>
       <c r="N13" t="inlineStr">
         <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="O13" t="inlineStr">
+        <is>
           <t>COMUNICACOES PARA INCLUSAO E TRANSFORMACAO</t>
         </is>
       </c>
@@ -1253,6 +1303,11 @@
       </c>
       <c r="N14" t="inlineStr">
         <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="O14" t="inlineStr">
+        <is>
           <t>POLITICA ECONOMICA PARA O CRESCIMENTO E DESENVOLVIMENTOSOCIO</t>
         </is>
       </c>
@@ -1318,6 +1373,11 @@
       </c>
       <c r="N15" t="inlineStr">
         <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="O15" t="inlineStr">
+        <is>
           <t>DESENVOLVIMENTO REGIONAL E ORDENAMENTO TERRITORIAL</t>
         </is>
       </c>
@@ -1383,6 +1443,11 @@
       </c>
       <c r="N16" t="inlineStr">
         <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="O16" t="inlineStr">
+        <is>
           <t>NEOINDUSTRIALIZACAO, AMBIENTE DE NEGOCIOS E PARTICIPACAO ECO</t>
         </is>
       </c>
@@ -1446,6 +1511,11 @@
           <t>model</t>
         </is>
       </c>
+      <c r="N17" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -1506,6 +1576,11 @@
           <t>model</t>
         </is>
       </c>
+      <c r="N18" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -1568,6 +1643,11 @@
       </c>
       <c r="N19" t="inlineStr">
         <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="O19" t="inlineStr">
+        <is>
           <t>SISTEMA FINANCEIRO DO FUTURO</t>
         </is>
       </c>
@@ -1633,6 +1713,11 @@
       </c>
       <c r="N20" t="inlineStr">
         <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="O20" t="inlineStr">
+        <is>
           <t>TRANSPARENCIA, INTEGRIDADE E ENFRENTAMENTO DA CORRUPCAO</t>
         </is>
       </c>
@@ -1698,6 +1783,11 @@
       </c>
       <c r="N21" t="inlineStr">
         <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="O21" t="inlineStr">
+        <is>
           <t>EDUCACAO SUPERIOR: QUALIDADE, DEMOCRACIA, EQUIDADE E SUSTENT</t>
         </is>
       </c>
@@ -1763,6 +1853,11 @@
       </c>
       <c r="N22" t="inlineStr">
         <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="O22" t="inlineStr">
+        <is>
           <t>PROMOCAO DO ACESSO A JUSTICA E DA DEFESA DOS DIREITOS</t>
         </is>
       </c>
@@ -1868,6 +1963,11 @@
       </c>
       <c r="N24" t="inlineStr">
         <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="O24" t="inlineStr">
+        <is>
           <t>PROGRAMA DE GESTAO E MANUTENCAO DO PODER EXECUTIVO</t>
         </is>
       </c>
@@ -1933,6 +2033,11 @@
       </c>
       <c r="N25" t="inlineStr">
         <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="O25" t="inlineStr">
+        <is>
           <t>OPERACOES ESPECIAIS: FINANCIAMENTOS COM RETORNO</t>
         </is>
       </c>
@@ -1998,6 +2103,11 @@
       </c>
       <c r="N26" t="inlineStr">
         <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="O26" t="inlineStr">
+        <is>
           <t>COOPERACAO DA DEFESA PARA O DESENVOLVIMENTO NACIONAL</t>
         </is>
       </c>
@@ -2063,6 +2173,11 @@
       </c>
       <c r="N27" t="inlineStr">
         <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="O27" t="inlineStr">
+        <is>
           <t>DEFESA NACIONAL</t>
         </is>
       </c>
@@ -2126,6 +2241,11 @@
           <t>model</t>
         </is>
       </c>
+      <c r="N28" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
@@ -2228,6 +2348,11 @@
       </c>
       <c r="N30" t="inlineStr">
         <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="O30" t="inlineStr">
+        <is>
           <t>PROGRAMA DE GESTAO E MANUTENCAO DO PODER EXECUTIVO</t>
         </is>
       </c>
@@ -2293,6 +2418,11 @@
       </c>
       <c r="N31" t="inlineStr">
         <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="O31" t="inlineStr">
+        <is>
           <t>GESTAO DE RISCOS E DE DESASTRES</t>
         </is>
       </c>
@@ -2358,6 +2488,11 @@
       </c>
       <c r="N32" t="inlineStr">
         <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="O32" t="inlineStr">
+        <is>
           <t>PROMOCAO DO ACESSO A JUSTICA E DA DEFESA DOS DIREITOS</t>
         </is>
       </c>
@@ -2423,6 +2558,11 @@
       </c>
       <c r="N33" t="inlineStr">
         <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="O33" t="inlineStr">
+        <is>
           <t>SEGURANCA PUBLICA COM CIDADANIA</t>
         </is>
       </c>
@@ -2528,6 +2668,11 @@
       </c>
       <c r="N35" t="inlineStr">
         <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="O35" t="inlineStr">
+        <is>
           <t>PROGRAMA DE GESTAO E MANUTENCAO DO PODER EXECUTIVO</t>
         </is>
       </c>
@@ -2591,6 +2736,11 @@
           <t>model</t>
         </is>
       </c>
+      <c r="N36" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
@@ -2651,6 +2801,11 @@
           <t>model</t>
         </is>
       </c>
+      <c r="N37" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
@@ -2753,6 +2908,11 @@
       </c>
       <c r="N39" t="inlineStr">
         <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="O39" t="inlineStr">
+        <is>
           <t>PROGRAMA DE GESTAO E MANUTENCAO DO PODER EXECUTIVO</t>
         </is>
       </c>
@@ -2818,6 +2978,11 @@
       </c>
       <c r="N40" t="inlineStr">
         <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="O40" t="inlineStr">
+        <is>
           <t>INCLUSAO SOCIOECONOMICA DO PUBLICO DO CADASTRO UNICO</t>
         </is>
       </c>
@@ -2883,6 +3048,11 @@
       </c>
       <c r="N41" t="inlineStr">
         <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="O41" t="inlineStr">
+        <is>
           <t>BOLSA FAMILIA: PROTECAO SOCIAL POR MEIO DA TRANSFERENCIA DE</t>
         </is>
       </c>
@@ -2948,6 +3118,11 @@
       </c>
       <c r="N42" t="inlineStr">
         <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="O42" t="inlineStr">
+        <is>
           <t>INCLUSAO DE FAMILIAS EM SITUACAO DE VULNERABILIDADE NO CADAS</t>
         </is>
       </c>
@@ -3013,6 +3188,11 @@
       </c>
       <c r="N43" t="inlineStr">
         <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="O43" t="inlineStr">
+        <is>
           <t>PROTECAO SOCIAL PELO SISTEMA UNICO DE ASSISTENCIA SOCIAL (SU</t>
         </is>
       </c>
@@ -3076,6 +3256,11 @@
           <t>model</t>
         </is>
       </c>
+      <c r="N44" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
@@ -3138,6 +3323,11 @@
       </c>
       <c r="N45" t="inlineStr">
         <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="O45" t="inlineStr">
+        <is>
           <t>CUIDADO E ACOLHIMENTO DE USUARIOS E DEPENDENTES DE ALCOOL E</t>
         </is>
       </c>
@@ -3203,6 +3393,11 @@
       </c>
       <c r="N46" t="inlineStr">
         <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="O46" t="inlineStr">
+        <is>
           <t>ESTRUTURACAO DA POLITICA NACIONAL DE CUIDADOS</t>
         </is>
       </c>
@@ -3268,6 +3463,11 @@
       </c>
       <c r="N47" t="inlineStr">
         <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="O47" t="inlineStr">
+        <is>
           <t>PROMOCAO DOS DIREITOS DAS PESSOAS COM DEFICIENCIA</t>
         </is>
       </c>
@@ -3373,6 +3573,11 @@
       </c>
       <c r="N49" t="inlineStr">
         <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="O49" t="inlineStr">
+        <is>
           <t>PROGRAMA DE GESTAO E MANUTENCAO DO PODER EXECUTIVO</t>
         </is>
       </c>
@@ -3436,6 +3641,11 @@
           <t>model</t>
         </is>
       </c>
+      <c r="N50" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
@@ -3498,6 +3708,11 @@
       </c>
       <c r="N51" t="inlineStr">
         <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="O51" t="inlineStr">
+        <is>
           <t>PREVIDENCIA SOCIAL: PROMOCAO, GARANTIA DE DIREITOS E CIDADAN</t>
         </is>
       </c>
@@ -3603,6 +3818,11 @@
       </c>
       <c r="N53" t="inlineStr">
         <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="O53" t="inlineStr">
+        <is>
           <t>PROGRAMA DE GESTAO E MANUTENCAO DO PODER EXECUTIVO</t>
         </is>
       </c>
@@ -3668,6 +3888,11 @@
       </c>
       <c r="N54" t="inlineStr">
         <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="O54" t="inlineStr">
+        <is>
           <t>OPERACOES ESPECIAIS: GESTAO DA PARTICIPACAO EM ORGANISMOS E</t>
         </is>
       </c>
@@ -3731,6 +3956,11 @@
           <t>model</t>
         </is>
       </c>
+      <c r="N55" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
@@ -3793,6 +4023,11 @@
       </c>
       <c r="N56" t="inlineStr">
         <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="O56" t="inlineStr">
+        <is>
           <t>QUALIFICACAO DA ASSISTENCIA FARMACEUTICA NO SISTEMA UNICO DE</t>
         </is>
       </c>
@@ -3858,6 +4093,11 @@
       </c>
       <c r="N57" t="inlineStr">
         <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="O57" t="inlineStr">
+        <is>
           <t>ATENCAO ESPECIALIZADA A SAUDE</t>
         </is>
       </c>
@@ -3923,6 +4163,11 @@
       </c>
       <c r="N58" t="inlineStr">
         <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="O58" t="inlineStr">
+        <is>
           <t>ATENCAO PRIMARIA A SAUDE</t>
         </is>
       </c>
@@ -3988,6 +4233,11 @@
       </c>
       <c r="N59" t="inlineStr">
         <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="O59" t="inlineStr">
+        <is>
           <t>PESQUISA, DESENVOLVIMENTO, INOVACAO, PRODUCAO E AVALIACAO DE</t>
         </is>
       </c>
@@ -4053,6 +4303,11 @@
       </c>
       <c r="N60" t="inlineStr">
         <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="O60" t="inlineStr">
+        <is>
           <t>GESTAO, TRABALHO, EDUCACAO E TRANSFORMACAO DIGITAL NA SAUDE</t>
         </is>
       </c>
@@ -4118,6 +4373,11 @@
       </c>
       <c r="N61" t="inlineStr">
         <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="O61" t="inlineStr">
+        <is>
           <t>SAUDE INDIGENA</t>
         </is>
       </c>
@@ -4183,6 +4443,11 @@
       </c>
       <c r="N62" t="inlineStr">
         <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="O62" t="inlineStr">
+        <is>
           <t>VIGILANCIA EM SAUDE E AMBIENTE</t>
         </is>
       </c>
@@ -4246,6 +4511,11 @@
           <t>model</t>
         </is>
       </c>
+      <c r="N63" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
@@ -4348,6 +4618,11 @@
       </c>
       <c r="N65" t="inlineStr">
         <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="O65" t="inlineStr">
+        <is>
           <t>PROGRAMA DE GESTAO E MANUTENCAO DO PODER EXECUTIVO</t>
         </is>
       </c>
@@ -4413,6 +4688,11 @@
       </c>
       <c r="N66" t="inlineStr">
         <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="O66" t="inlineStr">
+        <is>
           <t>OPERACOES ESPECIAIS: FINANCIAMENTOS COM RETORNO</t>
         </is>
       </c>
@@ -4478,6 +4758,11 @@
       </c>
       <c r="N67" t="inlineStr">
         <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="O67" t="inlineStr">
+        <is>
           <t>PROMOCAO DO TRABALHO DECENTE, EMPREGO E RENDA</t>
         </is>
       </c>
@@ -4543,6 +4828,11 @@
       </c>
       <c r="N68" t="inlineStr">
         <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="O68" t="inlineStr">
+        <is>
           <t>DESENVOLVIMENTO REGIONAL E ORDENAMENTO TERRITORIAL</t>
         </is>
       </c>
@@ -4606,6 +4896,11 @@
           <t>model</t>
         </is>
       </c>
+      <c r="N69" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
@@ -4708,6 +5003,11 @@
       </c>
       <c r="N71" t="inlineStr">
         <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="O71" t="inlineStr">
+        <is>
           <t>PROGRAMA DE GESTAO E MANUTENCAO DO PODER EXECUTIVO</t>
         </is>
       </c>
@@ -4773,6 +5073,11 @@
       </c>
       <c r="N72" t="inlineStr">
         <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="O72" t="inlineStr">
+        <is>
           <t>OPERACOES ESPECIAIS: FINANCIAMENTOS COM RETORNO</t>
         </is>
       </c>
@@ -4836,6 +5141,11 @@
           <t>model</t>
         </is>
       </c>
+      <c r="N73" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
@@ -4898,6 +5208,11 @@
       </c>
       <c r="N74" t="inlineStr">
         <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="O74" t="inlineStr">
+        <is>
           <t>EDUCACAO BASICA DEMOCRATICA, COM QUALIDADE E EQUIDADE</t>
         </is>
       </c>
@@ -4963,6 +5278,11 @@
       </c>
       <c r="N75" t="inlineStr">
         <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="O75" t="inlineStr">
+        <is>
           <t>EDUCACAO PROFISSIONAL E TECNOLOGICA QUE TRANSFORMA</t>
         </is>
       </c>
@@ -5028,6 +5348,11 @@
       </c>
       <c r="N76" t="inlineStr">
         <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="O76" t="inlineStr">
+        <is>
           <t>EDUCACAO SUPERIOR: QUALIDADE, DEMOCRACIA, EQUIDADE E SUSTENT</t>
         </is>
       </c>
@@ -5133,6 +5458,11 @@
       </c>
       <c r="N78" t="inlineStr">
         <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="O78" t="inlineStr">
+        <is>
           <t>PROGRAMA DE GESTAO E MANUTENCAO DO PODER EXECUTIVO</t>
         </is>
       </c>
@@ -5196,6 +5526,11 @@
           <t>model</t>
         </is>
       </c>
+      <c r="N79" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
@@ -5298,6 +5633,11 @@
       </c>
       <c r="N81" t="inlineStr">
         <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="O81" t="inlineStr">
+        <is>
           <t>PROGRAMA DE GESTAO E MANUTENCAO DO PODER EXECUTIVO</t>
         </is>
       </c>
@@ -5363,6 +5703,11 @@
       </c>
       <c r="N82" t="inlineStr">
         <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="O82" t="inlineStr">
+        <is>
           <t>PROTECAO DE TERRAS INDIGENAS, GESTAO TERRITORIAL E ETNODESEN</t>
         </is>
       </c>
@@ -5428,6 +5773,11 @@
       </c>
       <c r="N83" t="inlineStr">
         <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="O83" t="inlineStr">
+        <is>
           <t>OPERACOES ESPECIAIS: GESTAO DA PARTICIPACAO EM ORGANISMOS E</t>
         </is>
       </c>
@@ -5493,6 +5843,11 @@
       </c>
       <c r="N84" t="inlineStr">
         <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="O84" t="inlineStr">
+        <is>
           <t>RECONSTRUCAO, AMPLIACAO E APROFUNDAMENTO DA PARTICIPACAO SOC</t>
         </is>
       </c>
@@ -5558,6 +5913,11 @@
       </c>
       <c r="N85" t="inlineStr">
         <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="O85" t="inlineStr">
+        <is>
           <t>DEMARCACAO E GESTAO DOS TERRITORIOS INDIGENAS PARA O BEM VIV</t>
         </is>
       </c>
@@ -5623,6 +5983,11 @@
       </c>
       <c r="N86" t="inlineStr">
         <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="O86" t="inlineStr">
+        <is>
           <t>PROMOCAO DO ACESSO A JUSTICA E DA DEFESA DOS DIREITOS</t>
         </is>
       </c>
@@ -5688,6 +6053,11 @@
       </c>
       <c r="N87" t="inlineStr">
         <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="O87" t="inlineStr">
+        <is>
           <t>SEGURANCA PUBLICA COM CIDADANIA</t>
         </is>
       </c>
@@ -5753,6 +6123,11 @@
       </c>
       <c r="N88" t="inlineStr">
         <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="O88" t="inlineStr">
+        <is>
           <t>JUVENTUDE: DIREITOS, PARTICIPACAO E BEM VIVER</t>
         </is>
       </c>
@@ -5818,6 +6193,11 @@
       </c>
       <c r="N89" t="inlineStr">
         <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="O89" t="inlineStr">
+        <is>
           <t>IGUALDADE DE DECISAO E PODER PARA MULHERES</t>
         </is>
       </c>
@@ -5881,6 +6261,11 @@
           <t>model</t>
         </is>
       </c>
+      <c r="N90" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
@@ -5943,6 +6328,11 @@
       </c>
       <c r="N91" t="inlineStr">
         <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="O91" t="inlineStr">
+        <is>
           <t>AUTONOMIA ECONOMICA DAS MULHERES</t>
         </is>
       </c>
@@ -6008,6 +6398,11 @@
       </c>
       <c r="N92" t="inlineStr">
         <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="O92" t="inlineStr">
+        <is>
           <t>POLITICAS PARA QUILOMBOLAS, COMUNIDADES TRADICIONAIS DEMATRI</t>
         </is>
       </c>
@@ -6071,6 +6466,11 @@
           <t>model</t>
         </is>
       </c>
+      <c r="N93" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
@@ -6133,6 +6533,11 @@
       </c>
       <c r="N94" t="inlineStr">
         <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="O94" t="inlineStr">
+        <is>
           <t>PROMOCAO DA IGUALDADE ETNICO-RACIAL, COMBATE E SUPERACAO DO</t>
         </is>
       </c>
@@ -6198,6 +6603,11 @@
       </c>
       <c r="N95" t="inlineStr">
         <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="O95" t="inlineStr">
+        <is>
           <t>PROMOCAO DOS DIREITOS DAS PESSOAS COM DEFICIENCIA</t>
         </is>
       </c>
@@ -6263,6 +6673,11 @@
       </c>
       <c r="N96" t="inlineStr">
         <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="O96" t="inlineStr">
+        <is>
           <t>PROMOCAO E DEFESA DOS DIREITOS DAS PESSOAS LGBTQIA+</t>
         </is>
       </c>
@@ -6328,6 +6743,11 @@
       </c>
       <c r="N97" t="inlineStr">
         <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="O97" t="inlineStr">
+        <is>
           <t>PROGRAMA NACIONAL DE PROMOCAO DOS DIREITOS DA POPULACAOEM SI</t>
         </is>
       </c>
@@ -6393,6 +6813,11 @@
       </c>
       <c r="N98" t="inlineStr">
         <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="O98" t="inlineStr">
+        <is>
           <t>PROMOCAO DO DIREITO DE ENVELHECER E DOS DIREITOS HUMANOS DA</t>
         </is>
       </c>
@@ -6458,6 +6883,11 @@
       </c>
       <c r="N99" t="inlineStr">
         <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="O99" t="inlineStr">
+        <is>
           <t>PROMOCAO E PROTECAO INTEGRAL DOS DIREITOS HUMANOS DE CRIANCA</t>
         </is>
       </c>
@@ -6523,6 +6953,11 @@
       </c>
       <c r="N100" t="inlineStr">
         <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="O100" t="inlineStr">
+        <is>
           <t>PROMOCAO DA CIDADANIA, DEFESA DE DIREITOS HUMANOS E REPARACA</t>
         </is>
       </c>
@@ -6588,6 +7023,11 @@
       </c>
       <c r="N101" t="inlineStr">
         <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="O101" t="inlineStr">
+        <is>
           <t>DIREITOS PLURIETNICOS CULTURAIS E SOCIAIS PARA O PLENO EXERC</t>
         </is>
       </c>
@@ -6693,6 +7133,11 @@
       </c>
       <c r="N103" t="inlineStr">
         <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="O103" t="inlineStr">
+        <is>
           <t>PROGRAMA DE GESTAO E MANUTENCAO DO PODER EXECUTIVO</t>
         </is>
       </c>
@@ -6758,6 +7203,11 @@
       </c>
       <c r="N104" t="inlineStr">
         <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="O104" t="inlineStr">
+        <is>
           <t>DESENVOLVIMENTO REGIONAL E ORDENAMENTO TERRITORIAL</t>
         </is>
       </c>
@@ -6823,6 +7273,11 @@
       </c>
       <c r="N105" t="inlineStr">
         <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="O105" t="inlineStr">
+        <is>
           <t>GESTAO DE RISCOS E DE DESASTRES</t>
         </is>
       </c>
@@ -6886,6 +7341,11 @@
           <t>model</t>
         </is>
       </c>
+      <c r="N106" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
     </row>
     <row r="107">
       <c r="A107" t="inlineStr">
@@ -6946,6 +7406,11 @@
           <t>model</t>
         </is>
       </c>
+      <c r="N107" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
     </row>
     <row r="108">
       <c r="A108" t="inlineStr">
@@ -7006,6 +7471,11 @@
           <t>model</t>
         </is>
       </c>
+      <c r="N108" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
     </row>
     <row r="109">
       <c r="A109" t="inlineStr">
@@ -7066,6 +7536,11 @@
           <t>model</t>
         </is>
       </c>
+      <c r="N109" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
     </row>
     <row r="110">
       <c r="A110" t="inlineStr">
@@ -7166,6 +7641,11 @@
           <t>model</t>
         </is>
       </c>
+      <c r="N111" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
     </row>
     <row r="112">
       <c r="A112" t="inlineStr">
@@ -7226,6 +7706,11 @@
           <t>model</t>
         </is>
       </c>
+      <c r="N112" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
     </row>
     <row r="113">
       <c r="A113" t="inlineStr">
@@ -7328,6 +7813,11 @@
       </c>
       <c r="N114" t="inlineStr">
         <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="O114" t="inlineStr">
+        <is>
           <t>GESTAO DE RISCOS E DE DESASTRES</t>
         </is>
       </c>
@@ -7393,6 +7883,11 @@
       </c>
       <c r="N115" t="inlineStr">
         <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="O115" t="inlineStr">
+        <is>
           <t>RECURSOS HIDRICOS: AGUA EM QUANTIDADE E QUALIDADE PARA SEMPR</t>
         </is>
       </c>
@@ -7456,6 +7951,11 @@
           <t>model</t>
         </is>
       </c>
+      <c r="N116" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
     </row>
     <row r="117">
       <c r="A117" t="inlineStr">
@@ -7558,6 +8058,11 @@
       </c>
       <c r="N118" t="inlineStr">
         <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="O118" t="inlineStr">
+        <is>
           <t>PROGRAMA DE GESTAO E MANUTENCAO DO PODER EXECUTIVO</t>
         </is>
       </c>
@@ -7623,6 +8128,11 @@
       </c>
       <c r="N119" t="inlineStr">
         <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="O119" t="inlineStr">
+        <is>
           <t>ENFRENTAMENTO DA EMERGENCIA CLIMATICA</t>
         </is>
       </c>
@@ -7688,6 +8198,11 @@
       </c>
       <c r="N120" t="inlineStr">
         <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="O120" t="inlineStr">
+        <is>
           <t>BIOECONOMIA PARA UM NOVO CICLO DE PROSPERIDADE</t>
         </is>
       </c>
@@ -7751,6 +8266,11 @@
           <t>model</t>
         </is>
       </c>
+      <c r="N121" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
     </row>
     <row r="122">
       <c r="A122" t="inlineStr">
@@ -7813,6 +8333,11 @@
       </c>
       <c r="N122" t="inlineStr">
         <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="O122" t="inlineStr">
+        <is>
           <t>GESTAO DE RISCOS E DE DESASTRES</t>
         </is>
       </c>
@@ -7878,6 +8403,11 @@
       </c>
       <c r="N123" t="inlineStr">
         <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="O123" t="inlineStr">
+        <is>
           <t>RECURSOS HIDRICOS: AGUA EM QUANTIDADE E QUALIDADE PARA SEMPR</t>
         </is>
       </c>
@@ -7941,6 +8471,11 @@
           <t>model</t>
         </is>
       </c>
+      <c r="N124" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
     </row>
     <row r="125">
       <c r="A125" t="inlineStr">
@@ -8003,6 +8538,11 @@
       </c>
       <c r="N125" t="inlineStr">
         <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="O125" t="inlineStr">
+        <is>
           <t>EDUCACAO SUPERIOR: QUALIDADE, DEMOCRACIA, EQUIDADE E SUSTENT</t>
         </is>
       </c>
@@ -8068,6 +8608,11 @@
       </c>
       <c r="N126" t="inlineStr">
         <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="O126" t="inlineStr">
+        <is>
           <t>PROTECAO E RECUPERACAO DA BIODIVERSIDADE E COMBATE AO DESMAT</t>
         </is>
       </c>
@@ -8173,6 +8718,11 @@
       </c>
       <c r="N128" t="inlineStr">
         <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="O128" t="inlineStr">
+        <is>
           <t>PROGRAMA DE GESTAO E MANUTENCAO DO PODER EXECUTIVO</t>
         </is>
       </c>
@@ -8238,6 +8788,11 @@
       </c>
       <c r="N129" t="inlineStr">
         <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="O129" t="inlineStr">
+        <is>
           <t>OPERACOES ESPECIAIS: FINANCIAMENTOS COM RETORNO</t>
         </is>
       </c>
@@ -8301,6 +8856,11 @@
           <t>model</t>
         </is>
       </c>
+      <c r="N130" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
     </row>
     <row r="131">
       <c r="A131" t="inlineStr">
@@ -8363,6 +8923,11 @@
       </c>
       <c r="N131" t="inlineStr">
         <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="O131" t="inlineStr">
+        <is>
           <t>ENFRENTAMENTO DA EMERGENCIA CLIMATICA</t>
         </is>
       </c>
@@ -8428,6 +8993,11 @@
       </c>
       <c r="N132" t="inlineStr">
         <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="O132" t="inlineStr">
+        <is>
           <t>CIENCIA, TECNOLOGIA E INOVACAO PARA O DESENVOLVIMENTO SOCIAL</t>
         </is>
       </c>
@@ -8491,6 +9061,11 @@
           <t>model</t>
         </is>
       </c>
+      <c r="N133" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
     </row>
     <row r="134">
       <c r="A134" t="inlineStr">
@@ -8553,6 +9128,11 @@
       </c>
       <c r="N134" t="inlineStr">
         <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="O134" t="inlineStr">
+        <is>
           <t>PROGRAMA ESPACIAL BRASILEIRO</t>
         </is>
       </c>
@@ -8618,6 +9198,11 @@
       </c>
       <c r="N135" t="inlineStr">
         <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="O135" t="inlineStr">
+        <is>
           <t>CONSOLIDACAO DO SISTEMA NACIONAL DE CIENCIA, TECNOLOGIAE INO</t>
         </is>
       </c>
@@ -8683,6 +9268,11 @@
       </c>
       <c r="N136" t="inlineStr">
         <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="O136" t="inlineStr">
+        <is>
           <t>DESENVOLVIMENTO REGIONAL E ORDENAMENTO TERRITORIAL</t>
         </is>
       </c>
@@ -8748,6 +9338,11 @@
       </c>
       <c r="N137" t="inlineStr">
         <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="O137" t="inlineStr">
+        <is>
           <t>GESTAO DE RISCOS E DE DESASTRES</t>
         </is>
       </c>
@@ -8813,6 +9408,11 @@
       </c>
       <c r="N138" t="inlineStr">
         <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="O138" t="inlineStr">
+        <is>
           <t>INOVACAO NAS EMPRESAS PARA UMA NOVA INDUSTRIALIZACAO</t>
         </is>
       </c>
@@ -8876,6 +9476,11 @@
           <t>model</t>
         </is>
       </c>
+      <c r="N139" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
     </row>
     <row r="140">
       <c r="A140" t="inlineStr">
@@ -8938,6 +9543,11 @@
       </c>
       <c r="N140" t="inlineStr">
         <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="O140" t="inlineStr">
+        <is>
           <t>PROTECAO E RECUPERACAO DA BIODIVERSIDADE E COMBATE AO DESMAT</t>
         </is>
       </c>
@@ -9043,6 +9653,11 @@
       </c>
       <c r="N142" t="inlineStr">
         <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="O142" t="inlineStr">
+        <is>
           <t>PROGRAMA DE GESTAO E MANUTENCAO DO PODER EXECUTIVO</t>
         </is>
       </c>
@@ -9108,6 +9723,11 @@
       </c>
       <c r="N143" t="inlineStr">
         <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="O143" t="inlineStr">
+        <is>
           <t>OPERACOES ESPECIAIS: FINANCIAMENTOS COM RETORNO</t>
         </is>
       </c>
@@ -9171,6 +9791,11 @@
           <t>model</t>
         </is>
       </c>
+      <c r="N144" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
     </row>
     <row r="145">
       <c r="A145" t="inlineStr">
@@ -9231,6 +9856,11 @@
           <t>model</t>
         </is>
       </c>
+      <c r="N145" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
     </row>
     <row r="146">
       <c r="A146" t="inlineStr">
@@ -9291,6 +9921,11 @@
           <t>model</t>
         </is>
       </c>
+      <c r="N146" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
     </row>
     <row r="147">
       <c r="A147" t="inlineStr">
@@ -9351,6 +9986,11 @@
           <t>model</t>
         </is>
       </c>
+      <c r="N147" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
     </row>
     <row r="148">
       <c r="A148" t="inlineStr">
@@ -9413,6 +10053,11 @@
       </c>
       <c r="N148" t="inlineStr">
         <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="O148" t="inlineStr">
+        <is>
           <t>DESENVOLVIMENTO REGIONAL E ORDENAMENTO TERRITORIAL</t>
         </is>
       </c>
@@ -9478,6 +10123,11 @@
       </c>
       <c r="N149" t="inlineStr">
         <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="O149" t="inlineStr">
+        <is>
           <t>RECURSOS HIDRICOS: AGUA EM QUANTIDADE E QUALIDADE PARA SEMPR</t>
         </is>
       </c>
@@ -9541,6 +10191,11 @@
           <t>model</t>
         </is>
       </c>
+      <c r="N150" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
     </row>
     <row r="151">
       <c r="A151" t="inlineStr">
@@ -9601,6 +10256,11 @@
           <t>model</t>
         </is>
       </c>
+      <c r="N151" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
     </row>
     <row r="152">
       <c r="A152" t="inlineStr">
@@ -9703,6 +10363,11 @@
       </c>
       <c r="N153" t="inlineStr">
         <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="O153" t="inlineStr">
+        <is>
           <t>PROGRAMA DE GESTAO E MANUTENCAO DO PODER EXECUTIVO</t>
         </is>
       </c>
@@ -9766,6 +10431,11 @@
           <t>model</t>
         </is>
       </c>
+      <c r="N154" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
     </row>
     <row r="155">
       <c r="A155" t="inlineStr">
@@ -9828,6 +10498,11 @@
       </c>
       <c r="N155" t="inlineStr">
         <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="O155" t="inlineStr">
+        <is>
           <t>GOVERNANCA FUNDIARIA, REFORMA AGRARIA E REGULARIZACAO DE TER</t>
         </is>
       </c>
@@ -9891,6 +10566,11 @@
           <t>model</t>
         </is>
       </c>
+      <c r="N156" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
     </row>
     <row r="157">
       <c r="A157" t="inlineStr">
@@ -9993,6 +10673,11 @@
       </c>
       <c r="N158" t="inlineStr">
         <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="O158" t="inlineStr">
+        <is>
           <t>PROGRAMA DE GESTAO E MANUTENCAO DO PODER EXECUTIVO</t>
         </is>
       </c>
@@ -10058,6 +10743,11 @@
       </c>
       <c r="N159" t="inlineStr">
         <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="O159" t="inlineStr">
+        <is>
           <t>GESTAO DE RISCOS E DE DESASTRES</t>
         </is>
       </c>
@@ -10123,6 +10813,11 @@
       </c>
       <c r="N160" t="inlineStr">
         <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="O160" t="inlineStr">
+        <is>
           <t>RECURSOS HIDRICOS: AGUA EM QUANTIDADE E QUALIDADE PARA SEMPR</t>
         </is>
       </c>
@@ -10188,6 +10883,11 @@
       </c>
       <c r="N161" t="inlineStr">
         <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="O161" t="inlineStr">
+        <is>
           <t>NEOINDUSTRIALIZACAO, AMBIENTE DE NEGOCIOS E PARTICIPACAO ECO</t>
         </is>
       </c>
@@ -10251,6 +10951,11 @@
           <t>model</t>
         </is>
       </c>
+      <c r="N162" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
     </row>
     <row r="163">
       <c r="A163" t="inlineStr">
@@ -10311,6 +11016,11 @@
           <t>model</t>
         </is>
       </c>
+      <c r="N163" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
     </row>
     <row r="164">
       <c r="A164" t="inlineStr">
@@ -10413,6 +11123,11 @@
       </c>
       <c r="N165" t="inlineStr">
         <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="O165" t="inlineStr">
+        <is>
           <t>PROGRAMA DE GESTAO E MANUTENCAO DO PODER EXECUTIVO</t>
         </is>
       </c>
@@ -10478,6 +11193,11 @@
       </c>
       <c r="N166" t="inlineStr">
         <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="O166" t="inlineStr">
+        <is>
           <t>OPERACOES ESPECIAIS: FINANCIAMENTOS COM RETORNO</t>
         </is>
       </c>
@@ -10541,6 +11261,11 @@
           <t>model</t>
         </is>
       </c>
+      <c r="N167" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
     </row>
     <row r="168">
       <c r="A168" t="inlineStr">
@@ -10601,6 +11326,11 @@
           <t>model</t>
         </is>
       </c>
+      <c r="N168" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
     </row>
     <row r="169">
       <c r="A169" t="inlineStr">
@@ -10663,6 +11393,11 @@
       </c>
       <c r="N169" t="inlineStr">
         <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="O169" t="inlineStr">
+        <is>
           <t>NEOINDUSTRIALIZACAO, AMBIENTE DE NEGOCIOS E PARTICIPACAO ECO</t>
         </is>
       </c>
@@ -10768,6 +11503,11 @@
       </c>
       <c r="N171" t="inlineStr">
         <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="O171" t="inlineStr">
+        <is>
           <t>PROGRAMA DE GESTAO E MANUTENCAO DO PODER EXECUTIVO</t>
         </is>
       </c>
@@ -10833,6 +11573,11 @@
       </c>
       <c r="N172" t="inlineStr">
         <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="O172" t="inlineStr">
+        <is>
           <t>COMUNICACOES PARA INCLUSAO E TRANSFORMACAO</t>
         </is>
       </c>
@@ -10938,6 +11683,11 @@
       </c>
       <c r="N174" t="inlineStr">
         <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="O174" t="inlineStr">
+        <is>
           <t>PROGRAMA DE GESTAO E MANUTENCAO DO PODER EXECUTIVO</t>
         </is>
       </c>
@@ -11001,6 +11751,11 @@
           <t>model</t>
         </is>
       </c>
+      <c r="N175" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
     </row>
     <row r="176">
       <c r="A176" t="inlineStr">
@@ -11061,6 +11816,11 @@
           <t>model</t>
         </is>
       </c>
+      <c r="N176" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
     </row>
     <row r="177">
       <c r="A177" t="inlineStr">
@@ -11121,6 +11881,11 @@
           <t>model</t>
         </is>
       </c>
+      <c r="N177" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
     </row>
     <row r="178">
       <c r="A178" t="inlineStr">
@@ -11181,6 +11946,11 @@
           <t>model</t>
         </is>
       </c>
+      <c r="N178" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
     </row>
     <row r="179">
       <c r="A179" t="inlineStr">
@@ -11283,6 +12053,11 @@
       </c>
       <c r="N180" t="inlineStr">
         <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="O180" t="inlineStr">
+        <is>
           <t>PROGRAMA DE GESTAO E MANUTENCAO DO PODER EXECUTIVO</t>
         </is>
       </c>
@@ -11346,6 +12121,11 @@
           <t>model</t>
         </is>
       </c>
+      <c r="N181" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
     </row>
     <row r="182">
       <c r="A182" t="inlineStr">
@@ -11408,6 +12188,11 @@
       </c>
       <c r="N182" t="inlineStr">
         <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="O182" t="inlineStr">
+        <is>
           <t>OPERACOES ESPECIAIS: GESTAO DA PARTICIPACAO EM ORGANISMOS E</t>
         </is>
       </c>
@@ -11471,6 +12256,11 @@
           <t>model</t>
         </is>
       </c>
+      <c r="N183" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
     </row>
     <row r="184">
       <c r="A184" t="inlineStr">
@@ -11531,6 +12321,11 @@
           <t>model</t>
         </is>
       </c>
+      <c r="N184" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
     </row>
     <row r="185">
       <c r="A185" t="inlineStr">
@@ -11591,6 +12386,11 @@
           <t>model</t>
         </is>
       </c>
+      <c r="N185" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
     </row>
     <row r="186">
       <c r="A186" t="inlineStr">
@@ -11651,6 +12451,11 @@
           <t>model</t>
         </is>
       </c>
+      <c r="N186" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
     </row>
     <row r="187">
       <c r="A187" t="inlineStr">
@@ -11711,6 +12516,11 @@
           <t>model</t>
         </is>
       </c>
+      <c r="N187" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
     </row>
     <row r="188">
       <c r="A188" t="inlineStr">
@@ -11813,6 +12623,11 @@
       </c>
       <c r="N189" t="inlineStr">
         <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="O189" t="inlineStr">
+        <is>
           <t>PROGRAMA DE GESTAO E MANUTENCAO DO PODER EXECUTIVO</t>
         </is>
       </c>
@@ -11878,6 +12693,11 @@
       </c>
       <c r="N190" t="inlineStr">
         <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="O190" t="inlineStr">
+        <is>
           <t>ESPORTE PARA A VIDA</t>
         </is>
       </c>
@@ -11983,6 +12803,11 @@
       </c>
       <c r="N192" t="inlineStr">
         <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="O192" t="inlineStr">
+        <is>
           <t>PROGRAMA DE GESTAO E MANUTENCAO DO PODER EXECUTIVO</t>
         </is>
       </c>
@@ -12048,6 +12873,11 @@
       </c>
       <c r="N193" t="inlineStr">
         <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="O193" t="inlineStr">
+        <is>
           <t>OPERACOES ESPECIAIS: CUMPRIMENTO DE SENTENCAS JUDICIAIS</t>
         </is>
       </c>
@@ -12113,6 +12943,11 @@
       </c>
       <c r="N194" t="inlineStr">
         <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="O194" t="inlineStr">
+        <is>
           <t>OPERACOES ESPECIAIS: FINANCIAMENTOS COM RETORNO</t>
         </is>
       </c>
@@ -12176,6 +13011,11 @@
           <t>model</t>
         </is>
       </c>
+      <c r="N195" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
     </row>
     <row r="196">
       <c r="A196" t="inlineStr">
@@ -12238,6 +13078,11 @@
       </c>
       <c r="N196" t="inlineStr">
         <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="O196" t="inlineStr">
+        <is>
           <t>OPERACOES ESPECIAIS: SERVICO DA DIVIDA INTERNA (JUROS EAMORT</t>
         </is>
       </c>
@@ -12303,6 +13148,11 @@
       </c>
       <c r="N197" t="inlineStr">
         <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="O197" t="inlineStr">
+        <is>
           <t>OPERACOES ESPECIAIS: SERVICO DA DIVIDA EXTERNA (JUROS EAMORT</t>
         </is>
       </c>
@@ -12368,6 +13218,11 @@
       </c>
       <c r="N198" t="inlineStr">
         <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="O198" t="inlineStr">
+        <is>
           <t>OPERACOES ESPECIAIS: REFINANCIAMENTO DA DIVIDA INTERNA</t>
         </is>
       </c>
@@ -12433,6 +13288,11 @@
       </c>
       <c r="N199" t="inlineStr">
         <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="O199" t="inlineStr">
+        <is>
           <t>OPERACOES ESPECIAIS: REFINANCIAMENTO DA DIVIDA EXTERNA</t>
         </is>
       </c>
@@ -12496,6 +13356,11 @@
           <t>model</t>
         </is>
       </c>
+      <c r="N200" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
     </row>
     <row r="201">
       <c r="A201" t="inlineStr">
@@ -12558,6 +13423,11 @@
       </c>
       <c r="N201" t="inlineStr">
         <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="O201" t="inlineStr">
+        <is>
           <t>OPERACOES ESPECIAIS: GESTAO DA PARTICIPACAO EM ORGANISMOS E</t>
         </is>
       </c>
@@ -12623,6 +13493,11 @@
       </c>
       <c r="N202" t="inlineStr">
         <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="O202" t="inlineStr">
+        <is>
           <t>OPERACOES ESPECIAIS - REMUNERACAO DE AGENTES FINANCEIROS</t>
         </is>
       </c>
@@ -12688,6 +13563,11 @@
       </c>
       <c r="N203" t="inlineStr">
         <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="O203" t="inlineStr">
+        <is>
           <t>OPERACOES ESPECIAIS - INTEGRALIZACAO DE COTAS EM BANCOSINTER</t>
         </is>
       </c>
@@ -12751,6 +13631,11 @@
           <t>model</t>
         </is>
       </c>
+      <c r="N204" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
     </row>
     <row r="205">
       <c r="A205" t="inlineStr">
@@ -12813,6 +13698,11 @@
       </c>
       <c r="N205" t="inlineStr">
         <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="O205" t="inlineStr">
+        <is>
           <t>DESENVOLVIMENTO REGIONAL E ORDENAMENTO TERRITORIAL</t>
         </is>
       </c>
@@ -12878,6 +13768,11 @@
       </c>
       <c r="N206" t="inlineStr">
         <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="O206" t="inlineStr">
+        <is>
           <t>GESTAO DE RISCOS E DE DESASTRES</t>
         </is>
       </c>
@@ -12941,6 +13836,11 @@
           <t>model</t>
         </is>
       </c>
+      <c r="N207" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
     </row>
     <row r="208">
       <c r="A208" t="inlineStr">
@@ -13003,6 +13903,11 @@
       </c>
       <c r="N208" t="inlineStr">
         <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="O208" t="inlineStr">
+        <is>
           <t>PROMOCAO DA CIDADANIA, DEFESA DE DIREITOS HUMANOS E REPARACA</t>
         </is>
       </c>
@@ -13108,6 +14013,11 @@
       </c>
       <c r="N210" t="inlineStr">
         <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="O210" t="inlineStr">
+        <is>
           <t>OPERACOES ESPECIAIS: CUMPRIMENTO DE SENTENCAS JUDICIAIS</t>
         </is>
       </c>
@@ -13172,6 +14082,11 @@
         </is>
       </c>
       <c r="N211" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="O211" t="inlineStr">
         <is>
           <t>RESERVA DE CONTINGENCIA</t>
         </is>

--- a/brazil/budget_layer_all_years.xlsx
+++ b/brazil/budget_layer_all_years.xlsx
@@ -18429,7 +18429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G2"/>
+  <dimension ref="A1:I2"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -18450,20 +18450,30 @@
       </c>
       <c r="D1" t="inlineStr">
         <is>
+          <t>grand_total</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>extracted_pct</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
+        <is>
           <t>gap_pct</t>
         </is>
       </c>
-      <c r="E1" t="inlineStr">
+      <c r="G1" t="inlineStr">
         <is>
           <t>basis</t>
         </is>
       </c>
-      <c r="F1" t="inlineStr">
+      <c r="H1" t="inlineStr">
         <is>
           <t>nested_heads</t>
         </is>
       </c>
-      <c r="G1" t="inlineStr">
+      <c r="I1" t="inlineStr">
         <is>
           <t>national</t>
         </is>
@@ -18481,18 +18491,18 @@
       <c r="C2" t="n">
         <v>5323334.271</v>
       </c>
-      <c r="D2" t="n">
+      <c r="F2" t="n">
         <v>0.01</v>
       </c>
-      <c r="E2" t="inlineStr">
+      <c r="G2" t="inlineStr">
         <is>
           <t>heads</t>
         </is>
       </c>
-      <c r="F2" t="n">
+      <c r="H2" t="n">
         <v>1</v>
       </c>
-      <c r="G2" t="n">
+      <c r="I2" t="n">
         <v>5323812.22</v>
       </c>
     </row>
@@ -19281,7 +19291,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F6"/>
+  <dimension ref="A1:F7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -19324,7 +19334,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>zero_amount_programme</t>
+          <t>no_grand_total</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -19332,19 +19342,9 @@
           <t>2024</t>
         </is>
       </c>
-      <c r="D2" t="inlineStr">
-        <is>
-          <t>02</t>
-        </is>
-      </c>
-      <c r="E2" t="inlineStr">
-        <is>
-          <t>0033</t>
-        </is>
-      </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>programme carries no money; a strategy matched only to lines like this reads as funded while receiving nothing</t>
+          <t>the document printed no grand total that stage 5 could find, so there is nothing to check the extraction's completeness against. Every share for FY2024 rests on the heads being all of them.</t>
         </is>
       </c>
     </row>
@@ -19366,12 +19366,12 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>02</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>0151</t>
+          <t>0033</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
@@ -19398,12 +19398,12 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>23</t>
+          <t>14</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>0909</t>
+          <t>0151</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
@@ -19430,12 +19430,12 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>28</t>
+          <t>23</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>1144</t>
+          <t>0909</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -19447,20 +19447,52 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
+          <t>MEDIUM</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>zero_amount_programme</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>2024</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>28</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>1144</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>programme carries no money; a strategy matched only to lines like this reads as funded while receiving nothing</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
           <t>INFO</t>
         </is>
       </c>
-      <c r="B6" t="inlineStr">
+      <c r="B7" t="inlineStr">
         <is>
           <t>national_total</t>
         </is>
       </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>2024</t>
-        </is>
-      </c>
-      <c r="F6" t="inlineStr">
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>2024</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
         <is>
           <t>national budget total = 5,323,812.2</t>
         </is>
